--- a/thesis/tables/algoritma_kullanım_listesi.xlsx
+++ b/thesis/tables/algoritma_kullanım_listesi.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mmeliht/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\URL-Phishing-Detection\thesis\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07D5810F-E389-E64F-9864-B5F659E41F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{563621FC-ABD3-4D54-A1C1-5BAAAEAB778B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,12 +31,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="277">
   <si>
     <t>Random Forest,</t>
   </si>
@@ -1026,7 +1029,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1073,6 +1076,12 @@
       <charset val="162"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1082,7 +1091,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1090,11 +1099,63 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1130,18 +1191,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1185,14 +1234,32 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1475,16 +1542,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K191"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.83203125" style="7" customWidth="1"/>
-    <col min="2" max="2" width="15.5" style="3" customWidth="1"/>
+    <col min="1" max="1" width="27.85546875" style="7" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" style="3" customWidth="1"/>
     <col min="3" max="3" width="27" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="41.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="41.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>12</v>
       </c>
@@ -1501,7 +1568,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="90" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" ht="99.75" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>177</v>
       </c>
@@ -1518,14 +1585,14 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="14" t="s">
+    <row r="3" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="29" t="s">
         <v>178</v>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="29">
         <v>2019</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="29" t="s">
         <v>24</v>
       </c>
       <c r="D3" s="5" t="s">
@@ -1535,10 +1602,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="14"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="29"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
       <c r="D4" s="5" t="s">
         <v>1</v>
       </c>
@@ -1546,10 +1613,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="14"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="29"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
       <c r="D5" s="5" t="s">
         <v>2</v>
       </c>
@@ -1557,10 +1624,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="14"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="29"/>
+      <c r="B6" s="29"/>
+      <c r="C6" s="29"/>
       <c r="D6" s="5" t="s">
         <v>3</v>
       </c>
@@ -1568,10 +1635,10 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="14"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="29"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="29"/>
       <c r="D7" s="5" t="s">
         <v>4</v>
       </c>
@@ -1579,14 +1646,14 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="14" t="s">
+    <row r="8" spans="1:5" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="29" t="s">
         <v>179</v>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="29">
         <v>2023</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="29" t="s">
         <v>24</v>
       </c>
       <c r="D8" s="5" t="s">
@@ -1596,10 +1663,10 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="14"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="29"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="29"/>
       <c r="D9" s="3" t="s">
         <v>0</v>
       </c>
@@ -1607,10 +1674,10 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
+    <row r="10" spans="1:5" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="29"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
       <c r="D10" s="5" t="s">
         <v>28</v>
       </c>
@@ -1618,10 +1685,10 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="14"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="29"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="29"/>
       <c r="D11" s="5" t="s">
         <v>29</v>
       </c>
@@ -1629,14 +1696,14 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="14" t="s">
+    <row r="12" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="29" t="s">
         <v>180</v>
       </c>
-      <c r="B12" s="14">
+      <c r="B12" s="29">
         <v>2022</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="29" t="s">
         <v>24</v>
       </c>
       <c r="D12" s="5" t="s">
@@ -1646,10 +1713,10 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
+    <row r="13" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="29"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="29"/>
       <c r="D13" s="5" t="s">
         <v>35</v>
       </c>
@@ -1657,10 +1724,10 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
+    <row r="14" spans="1:5" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="29"/>
+      <c r="B14" s="29"/>
+      <c r="C14" s="29"/>
       <c r="D14" s="5" t="s">
         <v>36</v>
       </c>
@@ -1668,10 +1735,10 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" s="14"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="29"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="29"/>
       <c r="D15" s="5" t="s">
         <v>15</v>
       </c>
@@ -1679,14 +1746,14 @@
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="14" t="s">
+    <row r="16" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="29" t="s">
         <v>181</v>
       </c>
-      <c r="B16" s="14">
+      <c r="B16" s="29">
         <v>2021</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" s="29" t="s">
         <v>24</v>
       </c>
       <c r="D16" s="5" t="s">
@@ -1696,10 +1763,10 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" s="14"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="29"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="29"/>
       <c r="D17" s="3" t="s">
         <v>42</v>
       </c>
@@ -1707,10 +1774,10 @@
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" s="14"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="29"/>
+      <c r="B18" s="29"/>
+      <c r="C18" s="29"/>
       <c r="D18" s="3" t="s">
         <v>43</v>
       </c>
@@ -1718,7 +1785,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="90" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" ht="99.75" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>182</v>
       </c>
@@ -1735,14 +1802,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="14" t="s">
+    <row r="20" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="29" t="s">
         <v>183</v>
       </c>
-      <c r="B20" s="13">
+      <c r="B20" s="30">
         <v>2023</v>
       </c>
-      <c r="C20" s="16" t="s">
+      <c r="C20" s="31" t="s">
         <v>50</v>
       </c>
       <c r="D20" s="3" t="s">
@@ -1752,10 +1819,10 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" s="15"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="16"/>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="32"/>
+      <c r="B21" s="30"/>
+      <c r="C21" s="31"/>
       <c r="D21" s="3" t="s">
         <v>51</v>
       </c>
@@ -1763,10 +1830,10 @@
         <v>54</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" s="15"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="16"/>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="32"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="31"/>
       <c r="D22" s="3" t="s">
         <v>52</v>
       </c>
@@ -1774,14 +1841,14 @@
         <v>55</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="14" t="s">
+    <row r="23" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="29" t="s">
         <v>184</v>
       </c>
-      <c r="B23" s="13">
+      <c r="B23" s="30">
         <v>2020</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="C23" s="31" t="s">
         <v>24</v>
       </c>
       <c r="D23" s="3" t="s">
@@ -1791,10 +1858,10 @@
         <v>56</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24" s="15"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="16"/>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="32"/>
+      <c r="B24" s="30"/>
+      <c r="C24" s="31"/>
       <c r="D24" s="3" t="s">
         <v>22</v>
       </c>
@@ -1802,14 +1869,14 @@
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25" s="14" t="s">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="29" t="s">
         <v>185</v>
       </c>
-      <c r="B25" s="13">
+      <c r="B25" s="30">
         <v>2019</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="C25" s="30" t="s">
         <v>58</v>
       </c>
       <c r="D25" s="3" t="s">
@@ -1819,10 +1886,10 @@
         <v>59</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A26" s="15"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="32"/>
+      <c r="B26" s="30"/>
+      <c r="C26" s="30"/>
       <c r="D26" s="3" t="s">
         <v>22</v>
       </c>
@@ -1830,7 +1897,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="105" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" ht="114" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>186</v>
       </c>
@@ -1847,7 +1914,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="120" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" ht="128.25" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>187</v>
       </c>
@@ -1864,7 +1931,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="105" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" ht="99.75" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>188</v>
       </c>
@@ -1881,7 +1948,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="135" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" ht="156.75" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>189</v>
       </c>
@@ -1898,7 +1965,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="135" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" ht="128.25" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>190</v>
       </c>
@@ -1915,14 +1982,14 @@
         <v>74</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A32" s="14" t="s">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="29" t="s">
         <v>191</v>
       </c>
-      <c r="B32" s="13">
+      <c r="B32" s="30">
         <v>2023</v>
       </c>
-      <c r="C32" s="13" t="s">
+      <c r="C32" s="30" t="s">
         <v>20</v>
       </c>
       <c r="D32" s="3" t="s">
@@ -1932,10 +1999,10 @@
         <v>76</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A33" s="15"/>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="32"/>
+      <c r="B33" s="30"/>
+      <c r="C33" s="30"/>
       <c r="D33" s="3" t="s">
         <v>1</v>
       </c>
@@ -1943,10 +2010,10 @@
         <v>77</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A34" s="15"/>
-      <c r="B34" s="13"/>
-      <c r="C34" s="13"/>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="32"/>
+      <c r="B34" s="30"/>
+      <c r="C34" s="30"/>
       <c r="D34" s="3" t="s">
         <v>52</v>
       </c>
@@ -1954,7 +2021,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
         <v>192</v>
       </c>
@@ -1971,14 +2038,14 @@
         <v>81</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A36" s="14" t="s">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="29" t="s">
         <v>193</v>
       </c>
-      <c r="B36" s="13">
+      <c r="B36" s="30">
         <v>2022</v>
       </c>
-      <c r="C36" s="13" t="s">
+      <c r="C36" s="30" t="s">
         <v>82</v>
       </c>
       <c r="D36" s="3" t="s">
@@ -1988,10 +2055,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A37" s="15"/>
-      <c r="B37" s="13"/>
-      <c r="C37" s="13"/>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="32"/>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
       <c r="D37" s="3" t="s">
         <v>83</v>
       </c>
@@ -1999,10 +2066,10 @@
         <v>85</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A38" s="15"/>
-      <c r="B38" s="13"/>
-      <c r="C38" s="13"/>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="32"/>
+      <c r="B38" s="30"/>
+      <c r="C38" s="30"/>
       <c r="D38" s="3" t="s">
         <v>21</v>
       </c>
@@ -2010,7 +2077,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="90" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5" ht="99.75" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>194</v>
       </c>
@@ -2027,14 +2094,14 @@
         <v>88</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A40" s="14" t="s">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="29" t="s">
         <v>195</v>
       </c>
-      <c r="B40" s="13">
+      <c r="B40" s="30">
         <v>2021</v>
       </c>
-      <c r="C40" s="13" t="s">
+      <c r="C40" s="30" t="s">
         <v>89</v>
       </c>
       <c r="D40" s="3" t="s">
@@ -2044,10 +2111,10 @@
         <v>86</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A41" s="15"/>
-      <c r="B41" s="13"/>
-      <c r="C41" s="13"/>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="32"/>
+      <c r="B41" s="30"/>
+      <c r="C41" s="30"/>
       <c r="D41" s="3" t="s">
         <v>176</v>
       </c>
@@ -2055,14 +2122,14 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="14" t="s">
+    <row r="42" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="29" t="s">
         <v>196</v>
       </c>
-      <c r="B42" s="13">
+      <c r="B42" s="30">
         <v>2020</v>
       </c>
-      <c r="C42" s="16" t="s">
+      <c r="C42" s="31" t="s">
         <v>90</v>
       </c>
       <c r="D42" s="3" t="s">
@@ -2072,10 +2139,10 @@
         <v>92</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A43" s="15"/>
-      <c r="B43" s="13"/>
-      <c r="C43" s="16"/>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="32"/>
+      <c r="B43" s="30"/>
+      <c r="C43" s="31"/>
       <c r="D43" s="3" t="s">
         <v>91</v>
       </c>
@@ -2083,14 +2150,14 @@
         <v>93</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="14" t="s">
+    <row r="44" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="29" t="s">
         <v>197</v>
       </c>
-      <c r="B44" s="13">
+      <c r="B44" s="30">
         <v>2020</v>
       </c>
-      <c r="C44" s="16" t="s">
+      <c r="C44" s="31" t="s">
         <v>24</v>
       </c>
       <c r="D44" s="3" t="s">
@@ -2100,10 +2167,10 @@
         <v>98</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A45" s="15"/>
-      <c r="B45" s="13"/>
-      <c r="C45" s="16"/>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="32"/>
+      <c r="B45" s="30"/>
+      <c r="C45" s="31"/>
       <c r="D45" s="3" t="s">
         <v>96</v>
       </c>
@@ -2111,10 +2178,10 @@
         <v>99</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A46" s="15"/>
-      <c r="B46" s="13"/>
-      <c r="C46" s="16"/>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="32"/>
+      <c r="B46" s="30"/>
+      <c r="C46" s="31"/>
       <c r="D46" s="3" t="s">
         <v>97</v>
       </c>
@@ -2122,14 +2189,14 @@
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="14" t="s">
+    <row r="47" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="29" t="s">
         <v>198</v>
       </c>
-      <c r="B47" s="13">
+      <c r="B47" s="30">
         <v>2022</v>
       </c>
-      <c r="C47" s="16" t="s">
+      <c r="C47" s="31" t="s">
         <v>101</v>
       </c>
       <c r="D47" s="3" t="s">
@@ -2139,10 +2206,10 @@
         <v>103</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A48" s="15"/>
-      <c r="B48" s="13"/>
-      <c r="C48" s="16"/>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="32"/>
+      <c r="B48" s="30"/>
+      <c r="C48" s="31"/>
       <c r="D48" s="3" t="s">
         <v>102</v>
       </c>
@@ -2150,14 +2217,14 @@
         <v>104</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="14" t="s">
+    <row r="49" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="29" t="s">
         <v>199</v>
       </c>
-      <c r="B49" s="13">
+      <c r="B49" s="30">
         <v>2017</v>
       </c>
-      <c r="C49" s="16" t="s">
+      <c r="C49" s="31" t="s">
         <v>101</v>
       </c>
       <c r="D49" s="3" t="s">
@@ -2167,10 +2234,10 @@
         <v>106</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A50" s="15"/>
-      <c r="B50" s="13"/>
-      <c r="C50" s="16"/>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="32"/>
+      <c r="B50" s="30"/>
+      <c r="C50" s="31"/>
       <c r="D50" s="3" t="s">
         <v>218</v>
       </c>
@@ -2178,10 +2245,10 @@
         <v>107</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A51" s="15"/>
-      <c r="B51" s="13"/>
-      <c r="C51" s="16"/>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="32"/>
+      <c r="B51" s="30"/>
+      <c r="C51" s="31"/>
       <c r="D51" s="3" t="s">
         <v>28</v>
       </c>
@@ -2189,10 +2256,10 @@
         <v>108</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A52" s="15"/>
-      <c r="B52" s="13"/>
-      <c r="C52" s="16"/>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="32"/>
+      <c r="B52" s="30"/>
+      <c r="C52" s="31"/>
       <c r="D52" s="3" t="s">
         <v>22</v>
       </c>
@@ -2200,14 +2267,14 @@
         <v>109</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="14" t="s">
+    <row r="53" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="29" t="s">
         <v>200</v>
       </c>
-      <c r="B53" s="13">
+      <c r="B53" s="30">
         <v>2022</v>
       </c>
-      <c r="C53" s="16" t="s">
+      <c r="C53" s="31" t="s">
         <v>101</v>
       </c>
       <c r="D53" s="3" t="s">
@@ -2217,10 +2284,10 @@
         <v>110</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A54" s="15"/>
-      <c r="B54" s="13"/>
-      <c r="C54" s="16"/>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="32"/>
+      <c r="B54" s="30"/>
+      <c r="C54" s="31"/>
       <c r="D54" s="3" t="s">
         <v>25</v>
       </c>
@@ -2228,10 +2295,10 @@
         <v>111</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A55" s="15"/>
-      <c r="B55" s="13"/>
-      <c r="C55" s="16"/>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="32"/>
+      <c r="B55" s="30"/>
+      <c r="C55" s="31"/>
       <c r="D55" s="3" t="s">
         <v>94</v>
       </c>
@@ -2239,10 +2306,10 @@
         <v>27</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A56" s="15"/>
-      <c r="B56" s="13"/>
-      <c r="C56" s="16"/>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="32"/>
+      <c r="B56" s="30"/>
+      <c r="C56" s="31"/>
       <c r="D56" s="3" t="s">
         <v>1</v>
       </c>
@@ -2250,10 +2317,10 @@
         <v>112</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A57" s="15"/>
-      <c r="B57" s="13"/>
-      <c r="C57" s="16"/>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="32"/>
+      <c r="B57" s="30"/>
+      <c r="C57" s="31"/>
       <c r="D57" s="3" t="s">
         <v>26</v>
       </c>
@@ -2261,7 +2328,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="105" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5" ht="99.75" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
         <v>201</v>
       </c>
@@ -2278,14 +2345,14 @@
         <v>115</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A59" s="14" t="s">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="29" t="s">
         <v>202</v>
       </c>
-      <c r="B59" s="13">
+      <c r="B59" s="30">
         <v>2022</v>
       </c>
-      <c r="C59" s="13" t="s">
+      <c r="C59" s="30" t="s">
         <v>67</v>
       </c>
       <c r="D59" s="3" t="s">
@@ -2295,10 +2362,10 @@
         <v>116</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A60" s="15"/>
-      <c r="B60" s="13"/>
-      <c r="C60" s="13"/>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="32"/>
+      <c r="B60" s="30"/>
+      <c r="C60" s="30"/>
       <c r="D60" s="3" t="s">
         <v>25</v>
       </c>
@@ -2306,10 +2373,10 @@
         <v>117</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A61" s="15"/>
-      <c r="B61" s="13"/>
-      <c r="C61" s="13"/>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="32"/>
+      <c r="B61" s="30"/>
+      <c r="C61" s="30"/>
       <c r="D61" s="3" t="s">
         <v>68</v>
       </c>
@@ -2317,10 +2384,10 @@
         <v>118</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A62" s="15"/>
-      <c r="B62" s="13"/>
-      <c r="C62" s="13"/>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="32"/>
+      <c r="B62" s="30"/>
+      <c r="C62" s="30"/>
       <c r="D62" s="3" t="s">
         <v>69</v>
       </c>
@@ -2328,7 +2395,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="120" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5" ht="114" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
         <v>203</v>
       </c>
@@ -2345,7 +2412,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="150" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5" ht="142.5" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
         <v>204</v>
       </c>
@@ -2362,7 +2429,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="135" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5" ht="128.25" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
         <v>205</v>
       </c>
@@ -2379,14 +2446,14 @@
         <v>126</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="14" t="s">
+    <row r="66" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="29" t="s">
         <v>206</v>
       </c>
-      <c r="B66" s="13">
+      <c r="B66" s="30">
         <v>2012</v>
       </c>
-      <c r="C66" s="16" t="s">
+      <c r="C66" s="31" t="s">
         <v>127</v>
       </c>
       <c r="D66" s="3" t="s">
@@ -2396,10 +2463,10 @@
         <v>129</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A67" s="15"/>
-      <c r="B67" s="13"/>
-      <c r="C67" s="16"/>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="32"/>
+      <c r="B67" s="30"/>
+      <c r="C67" s="31"/>
       <c r="D67" s="3" t="s">
         <v>128</v>
       </c>
@@ -2407,14 +2474,14 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="14" t="s">
+    <row r="68" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="B68" s="13">
+      <c r="B68" s="30">
         <v>2022</v>
       </c>
-      <c r="C68" s="16" t="s">
+      <c r="C68" s="31" t="s">
         <v>24</v>
       </c>
       <c r="D68" s="3" t="s">
@@ -2424,10 +2491,10 @@
         <v>130</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A69" s="15"/>
-      <c r="B69" s="13"/>
-      <c r="C69" s="16"/>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="32"/>
+      <c r="B69" s="30"/>
+      <c r="C69" s="31"/>
       <c r="D69" s="3" t="s">
         <v>113</v>
       </c>
@@ -2435,7 +2502,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="120" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:5" ht="128.25" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
         <v>208</v>
       </c>
@@ -2452,14 +2519,14 @@
         <v>134</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A71" s="14" t="s">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="B71" s="13">
+      <c r="B71" s="30">
         <v>2020</v>
       </c>
-      <c r="C71" s="13" t="s">
+      <c r="C71" s="30" t="s">
         <v>73</v>
       </c>
       <c r="D71" s="3" t="s">
@@ -2469,10 +2536,10 @@
         <v>135</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A72" s="15"/>
-      <c r="B72" s="13"/>
-      <c r="C72" s="13"/>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="32"/>
+      <c r="B72" s="30"/>
+      <c r="C72" s="30"/>
       <c r="D72" s="3" t="s">
         <v>141</v>
       </c>
@@ -2480,10 +2547,10 @@
         <v>136</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A73" s="15"/>
-      <c r="B73" s="13"/>
-      <c r="C73" s="13"/>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="32"/>
+      <c r="B73" s="30"/>
+      <c r="C73" s="30"/>
       <c r="D73" s="3" t="s">
         <v>142</v>
       </c>
@@ -2491,10 +2558,10 @@
         <v>137</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A74" s="15"/>
-      <c r="B74" s="13"/>
-      <c r="C74" s="13"/>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="32"/>
+      <c r="B74" s="30"/>
+      <c r="C74" s="30"/>
       <c r="D74" s="3" t="s">
         <v>139</v>
       </c>
@@ -2502,14 +2569,14 @@
         <v>217</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="14" t="s">
+    <row r="75" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="29" t="s">
         <v>210</v>
       </c>
-      <c r="B75" s="13">
+      <c r="B75" s="30">
         <v>2021</v>
       </c>
-      <c r="C75" s="16" t="s">
+      <c r="C75" s="31" t="s">
         <v>138</v>
       </c>
       <c r="D75" s="3" t="s">
@@ -2519,10 +2586,10 @@
         <v>144</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A76" s="15"/>
-      <c r="B76" s="13"/>
-      <c r="C76" s="16"/>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="32"/>
+      <c r="B76" s="30"/>
+      <c r="C76" s="31"/>
       <c r="D76" s="3" t="s">
         <v>143</v>
       </c>
@@ -2530,10 +2597,10 @@
         <v>145</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A77" s="15"/>
-      <c r="B77" s="13"/>
-      <c r="C77" s="16"/>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="32"/>
+      <c r="B77" s="30"/>
+      <c r="C77" s="31"/>
       <c r="D77" s="3" t="s">
         <v>147</v>
       </c>
@@ -2541,10 +2608,10 @@
         <v>146</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A78" s="15"/>
-      <c r="B78" s="13"/>
-      <c r="C78" s="16"/>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="32"/>
+      <c r="B78" s="30"/>
+      <c r="C78" s="31"/>
       <c r="D78" s="3" t="s">
         <v>148</v>
       </c>
@@ -2552,7 +2619,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="150" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:5" ht="142.5" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
         <v>211</v>
       </c>
@@ -2569,14 +2636,14 @@
         <v>151</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="14" t="s">
+    <row r="80" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="29" t="s">
         <v>212</v>
       </c>
-      <c r="B80" s="13">
+      <c r="B80" s="30">
         <v>2018</v>
       </c>
-      <c r="C80" s="16" t="s">
+      <c r="C80" s="31" t="s">
         <v>152</v>
       </c>
       <c r="D80" s="3" t="s">
@@ -2586,10 +2653,10 @@
         <v>155</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A81" s="15"/>
-      <c r="B81" s="13"/>
-      <c r="C81" s="16"/>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="32"/>
+      <c r="B81" s="30"/>
+      <c r="C81" s="31"/>
       <c r="D81" s="3" t="s">
         <v>153</v>
       </c>
@@ -2597,10 +2664,10 @@
         <v>156</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A82" s="15"/>
-      <c r="B82" s="13"/>
-      <c r="C82" s="16"/>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="32"/>
+      <c r="B82" s="30"/>
+      <c r="C82" s="31"/>
       <c r="D82" s="3" t="s">
         <v>154</v>
       </c>
@@ -2608,10 +2675,10 @@
         <v>157</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A83" s="15"/>
-      <c r="B83" s="13"/>
-      <c r="C83" s="16"/>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="32"/>
+      <c r="B83" s="30"/>
+      <c r="C83" s="31"/>
       <c r="D83" s="3" t="s">
         <v>17</v>
       </c>
@@ -2619,14 +2686,14 @@
         <v>158</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="14" t="s">
+    <row r="84" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="29" t="s">
         <v>213</v>
       </c>
-      <c r="B84" s="13">
+      <c r="B84" s="30">
         <v>2017</v>
       </c>
-      <c r="C84" s="16" t="s">
+      <c r="C84" s="31" t="s">
         <v>159</v>
       </c>
       <c r="D84" s="3" t="s">
@@ -2636,10 +2703,10 @@
         <v>162</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A85" s="15"/>
-      <c r="B85" s="13"/>
-      <c r="C85" s="16"/>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="32"/>
+      <c r="B85" s="30"/>
+      <c r="C85" s="31"/>
       <c r="D85" s="3" t="s">
         <v>160</v>
       </c>
@@ -2647,10 +2714,10 @@
         <v>163</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A86" s="15"/>
-      <c r="B86" s="13"/>
-      <c r="C86" s="16"/>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="32"/>
+      <c r="B86" s="30"/>
+      <c r="C86" s="31"/>
       <c r="D86" s="3" t="s">
         <v>25</v>
       </c>
@@ -2658,10 +2725,10 @@
         <v>164</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A87" s="15"/>
-      <c r="B87" s="13"/>
-      <c r="C87" s="16"/>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="32"/>
+      <c r="B87" s="30"/>
+      <c r="C87" s="31"/>
       <c r="D87" s="3" t="s">
         <v>161</v>
       </c>
@@ -2669,7 +2736,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="105" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:5" ht="114" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
         <v>214</v>
       </c>
@@ -2686,7 +2753,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="90" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:5" ht="114" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
         <v>215</v>
       </c>
@@ -2703,14 +2770,14 @@
         <v>171</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="14" t="s">
+    <row r="90" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="29" t="s">
         <v>216</v>
       </c>
-      <c r="B90" s="13">
+      <c r="B90" s="30">
         <v>2020</v>
       </c>
-      <c r="C90" s="13" t="s">
+      <c r="C90" s="30" t="s">
         <v>119</v>
       </c>
       <c r="D90" s="3" t="s">
@@ -2720,10 +2787,10 @@
         <v>37</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A91" s="14"/>
-      <c r="B91" s="13"/>
-      <c r="C91" s="13"/>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="29"/>
+      <c r="B91" s="30"/>
+      <c r="C91" s="30"/>
       <c r="D91" s="3" t="s">
         <v>25</v>
       </c>
@@ -2731,10 +2798,10 @@
         <v>173</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A92" s="14"/>
-      <c r="B92" s="13"/>
-      <c r="C92" s="13"/>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="29"/>
+      <c r="B92" s="30"/>
+      <c r="C92" s="30"/>
       <c r="D92" s="3" t="s">
         <v>34</v>
       </c>
@@ -2742,10 +2809,10 @@
         <v>174</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="14"/>
-      <c r="B93" s="13"/>
-      <c r="C93" s="13"/>
+    <row r="93" spans="1:5" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="29"/>
+      <c r="B93" s="30"/>
+      <c r="C93" s="30"/>
       <c r="D93" s="3" t="s">
         <v>172</v>
       </c>
@@ -2753,14 +2820,14 @@
         <v>175</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="14" t="s">
+    <row r="94" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="29" t="s">
         <v>224</v>
       </c>
-      <c r="B94" s="13">
+      <c r="B94" s="30">
         <v>2024</v>
       </c>
-      <c r="C94" s="13" t="s">
+      <c r="C94" s="30" t="s">
         <v>223</v>
       </c>
       <c r="D94" s="3" t="s">
@@ -2770,10 +2837,10 @@
         <v>221</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A95" s="14"/>
-      <c r="B95" s="13"/>
-      <c r="C95" s="13"/>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="29"/>
+      <c r="B95" s="30"/>
+      <c r="C95" s="30"/>
       <c r="D95" s="3" t="s">
         <v>219</v>
       </c>
@@ -2781,10 +2848,10 @@
         <v>220</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A96" s="14"/>
-      <c r="B96" s="13"/>
-      <c r="C96" s="13"/>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="29"/>
+      <c r="B96" s="30"/>
+      <c r="C96" s="30"/>
       <c r="D96" s="3" t="s">
         <v>4</v>
       </c>
@@ -2792,14 +2859,14 @@
         <v>222</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="14" t="s">
+    <row r="97" spans="1:5" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="29" t="s">
         <v>230</v>
       </c>
-      <c r="B97" s="13">
+      <c r="B97" s="30">
         <v>2024</v>
       </c>
-      <c r="C97" s="16" t="s">
+      <c r="C97" s="31" t="s">
         <v>231</v>
       </c>
       <c r="D97" s="3" t="s">
@@ -2809,10 +2876,10 @@
         <v>226</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A98" s="14"/>
-      <c r="B98" s="13"/>
-      <c r="C98" s="13"/>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="29"/>
+      <c r="B98" s="30"/>
+      <c r="C98" s="30"/>
       <c r="D98" s="3" t="s">
         <v>4</v>
       </c>
@@ -2820,10 +2887,10 @@
         <v>227</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A99" s="14"/>
-      <c r="B99" s="13"/>
-      <c r="C99" s="13"/>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="29"/>
+      <c r="B99" s="30"/>
+      <c r="C99" s="30"/>
       <c r="D99" s="3" t="s">
         <v>17</v>
       </c>
@@ -2831,10 +2898,10 @@
         <v>228</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A100" s="14"/>
-      <c r="B100" s="13"/>
-      <c r="C100" s="13"/>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="29"/>
+      <c r="B100" s="30"/>
+      <c r="C100" s="30"/>
       <c r="D100" s="3" t="s">
         <v>18</v>
       </c>
@@ -2842,14 +2909,14 @@
         <v>229</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="14" t="s">
+    <row r="101" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="29" t="s">
         <v>232</v>
       </c>
-      <c r="B101" s="13">
+      <c r="B101" s="30">
         <v>2024</v>
       </c>
-      <c r="C101" s="13" t="s">
+      <c r="C101" s="30" t="s">
         <v>233</v>
       </c>
       <c r="D101" s="3" t="s">
@@ -2859,10 +2926,10 @@
         <v>236</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A102" s="14"/>
-      <c r="B102" s="13"/>
-      <c r="C102" s="13"/>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="29"/>
+      <c r="B102" s="30"/>
+      <c r="C102" s="30"/>
       <c r="D102" s="3" t="s">
         <v>176</v>
       </c>
@@ -2870,10 +2937,10 @@
         <v>237</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A103" s="14"/>
-      <c r="B103" s="13"/>
-      <c r="C103" s="13"/>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" s="29"/>
+      <c r="B103" s="30"/>
+      <c r="C103" s="30"/>
       <c r="D103" s="3" t="s">
         <v>17</v>
       </c>
@@ -2881,10 +2948,10 @@
         <v>238</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A104" s="14"/>
-      <c r="B104" s="13"/>
-      <c r="C104" s="13"/>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" s="29"/>
+      <c r="B104" s="30"/>
+      <c r="C104" s="30"/>
       <c r="D104" s="3" t="s">
         <v>52</v>
       </c>
@@ -2892,10 +2959,10 @@
         <v>239</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A105" s="14"/>
-      <c r="B105" s="13"/>
-      <c r="C105" s="13"/>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" s="29"/>
+      <c r="B105" s="30"/>
+      <c r="C105" s="30"/>
       <c r="D105" s="3" t="s">
         <v>4</v>
       </c>
@@ -2903,10 +2970,10 @@
         <v>240</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A106" s="14"/>
-      <c r="B106" s="13"/>
-      <c r="C106" s="13"/>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" s="29"/>
+      <c r="B106" s="30"/>
+      <c r="C106" s="30"/>
       <c r="D106" s="3" t="s">
         <v>225</v>
       </c>
@@ -2914,10 +2981,10 @@
         <v>241</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A107" s="14"/>
-      <c r="B107" s="13"/>
-      <c r="C107" s="13"/>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" s="29"/>
+      <c r="B107" s="30"/>
+      <c r="C107" s="30"/>
       <c r="D107" s="3" t="s">
         <v>234</v>
       </c>
@@ -2925,10 +2992,10 @@
         <v>242</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A108" s="14"/>
-      <c r="B108" s="13"/>
-      <c r="C108" s="13"/>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" s="29"/>
+      <c r="B108" s="30"/>
+      <c r="C108" s="30"/>
       <c r="D108" s="3" t="s">
         <v>235</v>
       </c>
@@ -2936,14 +3003,14 @@
         <v>243</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="14" t="s">
+    <row r="109" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="29" t="s">
         <v>244</v>
       </c>
-      <c r="B109" s="13">
+      <c r="B109" s="30">
         <v>2024</v>
       </c>
-      <c r="C109" s="16" t="s">
+      <c r="C109" s="31" t="s">
         <v>231</v>
       </c>
       <c r="D109" s="3" t="s">
@@ -2953,10 +3020,10 @@
         <v>260</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A110" s="14"/>
-      <c r="B110" s="13"/>
-      <c r="C110" s="13"/>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" s="29"/>
+      <c r="B110" s="30"/>
+      <c r="C110" s="30"/>
       <c r="D110" s="3" t="s">
         <v>15</v>
       </c>
@@ -2964,10 +3031,10 @@
         <v>261</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A111" s="14"/>
-      <c r="B111" s="13"/>
-      <c r="C111" s="13"/>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" s="29"/>
+      <c r="B111" s="30"/>
+      <c r="C111" s="30"/>
       <c r="D111" s="3" t="s">
         <v>245</v>
       </c>
@@ -2975,14 +3042,14 @@
         <v>262</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="14" t="s">
+    <row r="112" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="29" t="s">
         <v>250</v>
       </c>
-      <c r="B112" s="13">
+      <c r="B112" s="30">
         <v>2025</v>
       </c>
-      <c r="C112" s="13"/>
+      <c r="C112" s="30"/>
       <c r="D112" s="3" t="s">
         <v>246</v>
       </c>
@@ -2990,10 +3057,10 @@
         <v>263</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A113" s="14"/>
-      <c r="B113" s="13"/>
-      <c r="C113" s="13"/>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" s="29"/>
+      <c r="B113" s="30"/>
+      <c r="C113" s="30"/>
       <c r="D113" s="3" t="s">
         <v>247</v>
       </c>
@@ -3001,10 +3068,10 @@
         <v>86</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A114" s="14"/>
-      <c r="B114" s="13"/>
-      <c r="C114" s="13"/>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" s="29"/>
+      <c r="B114" s="30"/>
+      <c r="C114" s="30"/>
       <c r="D114" s="3" t="s">
         <v>248</v>
       </c>
@@ -3012,10 +3079,10 @@
         <v>86</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A115" s="14"/>
-      <c r="B115" s="13"/>
-      <c r="C115" s="13"/>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" s="29"/>
+      <c r="B115" s="30"/>
+      <c r="C115" s="30"/>
       <c r="D115" s="3" t="s">
         <v>249</v>
       </c>
@@ -3023,14 +3090,14 @@
         <v>264</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A116" s="14" t="s">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" s="29" t="s">
         <v>253</v>
       </c>
-      <c r="B116" s="13">
+      <c r="B116" s="30">
         <v>2025</v>
       </c>
-      <c r="C116" s="13"/>
+      <c r="C116" s="30"/>
       <c r="D116" s="3" t="s">
         <v>161</v>
       </c>
@@ -3038,10 +3105,10 @@
         <v>265</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A117" s="14"/>
-      <c r="B117" s="13"/>
-      <c r="C117" s="13"/>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" s="29"/>
+      <c r="B117" s="30"/>
+      <c r="C117" s="30"/>
       <c r="D117" s="3" t="s">
         <v>4</v>
       </c>
@@ -3049,10 +3116,10 @@
         <v>175</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A118" s="14"/>
-      <c r="B118" s="13"/>
-      <c r="C118" s="13"/>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" s="29"/>
+      <c r="B118" s="30"/>
+      <c r="C118" s="30"/>
       <c r="D118" s="3" t="s">
         <v>251</v>
       </c>
@@ -3060,10 +3127,10 @@
         <v>266</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A119" s="14"/>
-      <c r="B119" s="13"/>
-      <c r="C119" s="13"/>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" s="29"/>
+      <c r="B119" s="30"/>
+      <c r="C119" s="30"/>
       <c r="D119" s="3" t="s">
         <v>15</v>
       </c>
@@ -3071,10 +3138,10 @@
         <v>267</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A120" s="14"/>
-      <c r="B120" s="13"/>
-      <c r="C120" s="13"/>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" s="29"/>
+      <c r="B120" s="30"/>
+      <c r="C120" s="30"/>
       <c r="D120" s="3" t="s">
         <v>252</v>
       </c>
@@ -3082,10 +3149,10 @@
         <v>268</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A121" s="14"/>
-      <c r="B121" s="13"/>
-      <c r="C121" s="13"/>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" s="29"/>
+      <c r="B121" s="30"/>
+      <c r="C121" s="30"/>
       <c r="D121" s="3" t="s">
         <v>176</v>
       </c>
@@ -3093,14 +3160,14 @@
         <v>267</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A122" s="14" t="s">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" s="29" t="s">
         <v>271</v>
       </c>
-      <c r="B122" s="13">
+      <c r="B122" s="30">
         <v>2025</v>
       </c>
-      <c r="C122" s="13"/>
+      <c r="C122" s="30"/>
       <c r="D122" s="3" t="s">
         <v>254</v>
       </c>
@@ -3108,10 +3175,10 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A123" s="14"/>
-      <c r="B123" s="13"/>
-      <c r="C123" s="13"/>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" s="29"/>
+      <c r="B123" s="30"/>
+      <c r="C123" s="30"/>
       <c r="D123" s="3" t="s">
         <v>52</v>
       </c>
@@ -3119,10 +3186,10 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A124" s="14"/>
-      <c r="B124" s="13"/>
-      <c r="C124" s="13"/>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" s="29"/>
+      <c r="B124" s="30"/>
+      <c r="C124" s="30"/>
       <c r="D124" s="3" t="s">
         <v>234</v>
       </c>
@@ -3130,10 +3197,10 @@
         <v>0.94</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A125" s="14"/>
-      <c r="B125" s="13"/>
-      <c r="C125" s="13"/>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125" s="29"/>
+      <c r="B125" s="30"/>
+      <c r="C125" s="30"/>
       <c r="D125" s="3" t="s">
         <v>15</v>
       </c>
@@ -3141,10 +3208,10 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A126" s="14"/>
-      <c r="B126" s="13"/>
-      <c r="C126" s="13"/>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" s="29"/>
+      <c r="B126" s="30"/>
+      <c r="C126" s="30"/>
       <c r="D126" s="3" t="s">
         <v>19</v>
       </c>
@@ -3152,10 +3219,10 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A127" s="14"/>
-      <c r="B127" s="13"/>
-      <c r="C127" s="13"/>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" s="29"/>
+      <c r="B127" s="30"/>
+      <c r="C127" s="30"/>
       <c r="D127" s="3" t="s">
         <v>18</v>
       </c>
@@ -3163,10 +3230,10 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A128" s="14"/>
-      <c r="B128" s="13"/>
-      <c r="C128" s="13"/>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A128" s="29"/>
+      <c r="B128" s="30"/>
+      <c r="C128" s="30"/>
       <c r="D128" s="3" t="s">
         <v>255</v>
       </c>
@@ -3174,10 +3241,10 @@
         <v>269</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A129" s="14"/>
-      <c r="B129" s="13"/>
-      <c r="C129" s="13"/>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129" s="29"/>
+      <c r="B129" s="30"/>
+      <c r="C129" s="30"/>
       <c r="D129" s="3" t="s">
         <v>256</v>
       </c>
@@ -3185,10 +3252,10 @@
         <v>0.92</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A130" s="14"/>
-      <c r="B130" s="13"/>
-      <c r="C130" s="13"/>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130" s="29"/>
+      <c r="B130" s="30"/>
+      <c r="C130" s="30"/>
       <c r="D130" s="3" t="s">
         <v>257</v>
       </c>
@@ -3196,10 +3263,10 @@
         <v>0.81</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A131" s="14"/>
-      <c r="B131" s="13"/>
-      <c r="C131" s="13"/>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131" s="29"/>
+      <c r="B131" s="30"/>
+      <c r="C131" s="30"/>
       <c r="D131" s="3" t="s">
         <v>258</v>
       </c>
@@ -3207,10 +3274,10 @@
         <v>270</v>
       </c>
     </row>
-    <row r="132" spans="1:5" ht="14" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A132" s="14"/>
-      <c r="B132" s="13"/>
-      <c r="C132" s="13"/>
+    <row r="132" spans="1:5" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="29"/>
+      <c r="B132" s="30"/>
+      <c r="C132" s="30"/>
       <c r="D132" s="3" t="s">
         <v>259</v>
       </c>
@@ -3218,14 +3285,14 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A133" s="14" t="s">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A133" s="29" t="s">
         <v>273</v>
       </c>
-      <c r="B133" s="13">
+      <c r="B133" s="30">
         <v>2025</v>
       </c>
-      <c r="C133" s="13"/>
+      <c r="C133" s="30"/>
       <c r="D133" s="3" t="s">
         <v>17</v>
       </c>
@@ -3233,10 +3300,10 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A134" s="14"/>
-      <c r="B134" s="13"/>
-      <c r="C134" s="13"/>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A134" s="29"/>
+      <c r="B134" s="30"/>
+      <c r="C134" s="30"/>
       <c r="D134" s="3" t="s">
         <v>15</v>
       </c>
@@ -3244,10 +3311,10 @@
         <v>0.81</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A135" s="14"/>
-      <c r="B135" s="13"/>
-      <c r="C135" s="13"/>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A135" s="29"/>
+      <c r="B135" s="30"/>
+      <c r="C135" s="30"/>
       <c r="D135" s="3" t="s">
         <v>16</v>
       </c>
@@ -3255,10 +3322,10 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A136" s="14"/>
-      <c r="B136" s="13"/>
-      <c r="C136" s="13"/>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136" s="29"/>
+      <c r="B136" s="30"/>
+      <c r="C136" s="30"/>
       <c r="D136" s="3" t="s">
         <v>272</v>
       </c>
@@ -3266,479 +3333,507 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A137" s="14" t="s">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137" s="29" t="s">
         <v>276</v>
       </c>
-      <c r="B137" s="13">
+      <c r="B137" s="30">
         <v>2026</v>
       </c>
-      <c r="C137" s="13"/>
+      <c r="C137" s="30"/>
       <c r="D137" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E137" s="19">
+      <c r="E137" s="15">
         <v>0.94</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A138" s="14"/>
-      <c r="B138" s="13"/>
-      <c r="C138" s="13"/>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138" s="29"/>
+      <c r="B138" s="30"/>
+      <c r="C138" s="30"/>
       <c r="D138" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E138" s="19">
+      <c r="E138" s="15">
         <v>0.95</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A139" s="14"/>
-      <c r="B139" s="13"/>
-      <c r="C139" s="13"/>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139" s="29"/>
+      <c r="B139" s="30"/>
+      <c r="C139" s="30"/>
       <c r="D139" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E139" s="19">
+      <c r="E139" s="15">
         <v>0.67</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A140" s="14"/>
-      <c r="B140" s="13"/>
-      <c r="C140" s="13"/>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A140" s="29"/>
+      <c r="B140" s="30"/>
+      <c r="C140" s="30"/>
       <c r="D140" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E140" s="19">
+      <c r="E140" s="15">
         <v>0.97</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A141" s="14"/>
-      <c r="B141" s="13"/>
-      <c r="C141" s="13"/>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A141" s="29"/>
+      <c r="B141" s="30"/>
+      <c r="C141" s="30"/>
       <c r="D141" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E141" s="19">
+      <c r="E141" s="15">
         <v>0.94</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A142" s="14"/>
-      <c r="B142" s="13"/>
-      <c r="C142" s="13"/>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A142" s="29"/>
+      <c r="B142" s="30"/>
+      <c r="C142" s="30"/>
       <c r="D142" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="E142" s="19">
+      <c r="E142" s="15">
         <v>0.96</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A143" s="14"/>
-      <c r="B143" s="13"/>
-      <c r="C143" s="13"/>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A143" s="29"/>
+      <c r="B143" s="30"/>
+      <c r="C143" s="30"/>
       <c r="D143" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="E143" s="19">
+      <c r="E143" s="15">
         <v>0.95</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="5"/>
-      <c r="E144" s="19"/>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E144" s="15"/>
+    </row>
+    <row r="145" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="5"/>
-      <c r="E145" s="19"/>
-    </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A146" s="5"/>
-      <c r="E146" s="19"/>
-    </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A147" s="5"/>
-      <c r="E147" s="19"/>
-    </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A148" s="18"/>
-    </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A149" s="32"/>
-      <c r="B149" s="18"/>
-      <c r="C149" s="34"/>
-      <c r="D149" s="18"/>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A150" s="33"/>
-      <c r="B150"/>
-      <c r="C150" s="17"/>
+      <c r="E145" s="15"/>
+    </row>
+    <row r="146" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A146" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" s="34">
+        <v>21</v>
+      </c>
+      <c r="C146" s="34">
+        <v>14.788732400000001</v>
+      </c>
+      <c r="E146" s="15"/>
+    </row>
+    <row r="147" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A147" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="B147" s="36">
+        <v>12</v>
+      </c>
+      <c r="C147" s="36">
+        <v>8.4507042299999995</v>
+      </c>
+      <c r="E147" s="15"/>
+    </row>
+    <row r="148" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A148" s="35" t="s">
+        <v>22</v>
+      </c>
+      <c r="B148" s="36">
+        <v>11</v>
+      </c>
+      <c r="C148" s="36">
+        <v>8.4507042299999995</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A149" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="B149" s="36">
+        <v>9</v>
+      </c>
+      <c r="C149" s="36">
+        <v>7.04225352</v>
+      </c>
+      <c r="D149" s="14"/>
+    </row>
+    <row r="150" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A150" s="35" t="s">
+        <v>176</v>
+      </c>
+      <c r="B150" s="36">
+        <v>7</v>
+      </c>
+      <c r="C150" s="36">
+        <v>4.92957746</v>
+      </c>
       <c r="D150"/>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A151" s="33"/>
-      <c r="B151"/>
-      <c r="C151" s="17"/>
+    <row r="151" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A151" s="35" t="s">
+        <v>52</v>
+      </c>
+      <c r="B151" s="36">
+        <v>6</v>
+      </c>
+      <c r="C151" s="36">
+        <v>4.92957746</v>
+      </c>
       <c r="D151"/>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A152" s="33"/>
-      <c r="B152"/>
-      <c r="C152" s="17"/>
+    <row r="152" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A152" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="B152" s="36">
+        <v>6</v>
+      </c>
+      <c r="C152" s="36">
+        <v>4.2253521100000002</v>
+      </c>
       <c r="D152"/>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A153" s="33"/>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A153" s="28"/>
       <c r="B153"/>
-      <c r="C153" s="17"/>
+      <c r="C153" s="13"/>
       <c r="D153"/>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A154" s="33"/>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A154" s="28"/>
       <c r="B154"/>
-      <c r="C154" s="17"/>
+      <c r="C154" s="13"/>
       <c r="D154"/>
       <c r="E154" s="3"/>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A155" s="33"/>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A155" s="28"/>
       <c r="B155"/>
-      <c r="C155" s="17"/>
+      <c r="C155" s="13"/>
       <c r="D155"/>
       <c r="E155" s="3"/>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A156" s="33"/>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A156" s="28"/>
       <c r="B156"/>
-      <c r="C156" s="17"/>
+      <c r="C156" s="13"/>
       <c r="D156"/>
       <c r="E156" s="3"/>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A157" s="33"/>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A157" s="28"/>
       <c r="B157"/>
-      <c r="C157" s="17"/>
+      <c r="C157" s="13"/>
       <c r="D157"/>
       <c r="E157" s="3"/>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A158" s="33"/>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A158" s="28"/>
       <c r="B158"/>
-      <c r="C158" s="17"/>
+      <c r="C158" s="13"/>
       <c r="D158"/>
       <c r="E158" s="3"/>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A159" s="33"/>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A159" s="28"/>
       <c r="B159"/>
-      <c r="C159" s="17"/>
+      <c r="C159" s="13"/>
       <c r="D159"/>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="3"/>
       <c r="B160"/>
-      <c r="C160" s="17"/>
+      <c r="C160" s="13"/>
       <c r="D160"/>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A161" s="21"/>
-      <c r="B161" s="30"/>
-      <c r="C161" s="29"/>
-    </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A162" s="21"/>
-      <c r="B162" s="30"/>
-      <c r="C162" s="29"/>
-    </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A163" s="21"/>
-      <c r="B163" s="30"/>
-      <c r="C163" s="29"/>
-    </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A164" s="21"/>
-      <c r="B164" s="30"/>
-      <c r="C164" s="29"/>
-    </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A165" s="21"/>
-      <c r="B165" s="30"/>
-      <c r="C165" s="29"/>
-    </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A161" s="17"/>
+      <c r="B161" s="26"/>
+      <c r="C161" s="25"/>
+    </row>
+    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A162" s="17"/>
+      <c r="B162" s="26"/>
+      <c r="C162" s="25"/>
+    </row>
+    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A163" s="17"/>
+      <c r="B163" s="26"/>
+      <c r="C163" s="25"/>
+    </row>
+    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A164" s="17"/>
+      <c r="B164" s="26"/>
+      <c r="C164" s="25"/>
+    </row>
+    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A165" s="17"/>
+      <c r="B165" s="26"/>
+      <c r="C165" s="25"/>
+    </row>
+    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A166" s="12"/>
       <c r="B166" s="8"/>
       <c r="C166" s="10"/>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A167" s="12"/>
       <c r="B167" s="8"/>
       <c r="C167" s="10"/>
     </row>
-    <row r="168" spans="1:11" ht="19" x14ac:dyDescent="0.2">
-      <c r="A168" s="31"/>
-      <c r="B168" s="24"/>
-      <c r="C168" s="25"/>
-      <c r="D168" s="26"/>
-      <c r="E168" s="26"/>
-    </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A169" s="26"/>
-      <c r="B169" s="24"/>
-      <c r="C169" s="25"/>
-      <c r="D169" s="26"/>
-      <c r="E169" s="26"/>
-    </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A170" s="22"/>
-      <c r="B170" s="22"/>
-      <c r="C170" s="22"/>
-      <c r="D170" s="22"/>
-      <c r="E170" s="22"/>
+    <row r="168" spans="1:11" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A168" s="27"/>
+      <c r="B168" s="20"/>
+      <c r="C168" s="21"/>
+      <c r="D168" s="22"/>
+      <c r="E168" s="22"/>
+    </row>
+    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A169" s="22"/>
+      <c r="B169" s="20"/>
+      <c r="C169" s="21"/>
+      <c r="D169" s="22"/>
+      <c r="E169" s="22"/>
+    </row>
+    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A170" s="18"/>
+      <c r="B170" s="18"/>
+      <c r="C170" s="18"/>
+      <c r="D170" s="18"/>
+      <c r="E170" s="18"/>
       <c r="G170" s="10"/>
       <c r="H170" s="10"/>
       <c r="I170" s="10"/>
       <c r="J170" s="10"/>
       <c r="K170" s="10"/>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A171" s="21"/>
-      <c r="B171" s="27"/>
-      <c r="C171" s="21"/>
-      <c r="D171" s="21"/>
-      <c r="E171" s="21"/>
+    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A171" s="17"/>
+      <c r="B171" s="23"/>
+      <c r="C171" s="17"/>
+      <c r="D171" s="17"/>
+      <c r="E171" s="17"/>
       <c r="G171" s="1"/>
       <c r="H171" s="1"/>
       <c r="I171" s="1"/>
       <c r="J171" s="1"/>
       <c r="K171" s="1"/>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A172" s="21"/>
-      <c r="B172" s="27"/>
-      <c r="C172" s="21"/>
-      <c r="D172" s="21"/>
-      <c r="E172" s="21"/>
+    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A172" s="17"/>
+      <c r="B172" s="23"/>
+      <c r="C172" s="17"/>
+      <c r="D172" s="17"/>
+      <c r="E172" s="17"/>
       <c r="G172" s="1"/>
       <c r="H172" s="1"/>
       <c r="I172" s="1"/>
       <c r="J172" s="1"/>
       <c r="K172" s="1"/>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A173" s="21"/>
-      <c r="B173" s="27"/>
-      <c r="C173" s="21"/>
-      <c r="D173" s="21"/>
-      <c r="E173" s="21"/>
+    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A173" s="17"/>
+      <c r="B173" s="23"/>
+      <c r="C173" s="17"/>
+      <c r="D173" s="17"/>
+      <c r="E173" s="17"/>
       <c r="G173" s="1"/>
       <c r="H173" s="1"/>
       <c r="I173" s="1"/>
       <c r="J173" s="1"/>
       <c r="K173" s="1"/>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A174" s="21"/>
-      <c r="B174" s="27"/>
-      <c r="C174" s="21"/>
-      <c r="D174" s="21"/>
-      <c r="E174" s="21"/>
+    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A174" s="17"/>
+      <c r="B174" s="23"/>
+      <c r="C174" s="17"/>
+      <c r="D174" s="17"/>
+      <c r="E174" s="17"/>
       <c r="G174" s="1"/>
       <c r="H174" s="1"/>
       <c r="I174" s="1"/>
       <c r="J174" s="1"/>
       <c r="K174" s="1"/>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A175" s="21"/>
-      <c r="B175" s="27"/>
-      <c r="C175" s="21"/>
-      <c r="D175" s="21"/>
-      <c r="E175" s="21"/>
+    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A175" s="17"/>
+      <c r="B175" s="23"/>
+      <c r="C175" s="17"/>
+      <c r="D175" s="17"/>
+      <c r="E175" s="17"/>
       <c r="G175" s="1"/>
       <c r="H175" s="1"/>
       <c r="I175" s="1"/>
       <c r="J175" s="1"/>
       <c r="K175" s="1"/>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A176" s="21"/>
-      <c r="B176" s="27"/>
-      <c r="C176" s="21"/>
-      <c r="D176" s="21"/>
-      <c r="E176" s="21"/>
+    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A176" s="17"/>
+      <c r="B176" s="23"/>
+      <c r="C176" s="17"/>
+      <c r="D176" s="17"/>
+      <c r="E176" s="17"/>
       <c r="G176" s="1"/>
       <c r="H176" s="1"/>
       <c r="I176" s="1"/>
       <c r="J176" s="1"/>
       <c r="K176" s="1"/>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A177" s="20"/>
-      <c r="B177" s="28"/>
-      <c r="C177" s="20"/>
-      <c r="D177" s="20"/>
-      <c r="E177" s="20"/>
+    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A177" s="16"/>
+      <c r="B177" s="24"/>
+      <c r="C177" s="16"/>
+      <c r="D177" s="16"/>
+      <c r="E177" s="16"/>
       <c r="G177" s="11"/>
       <c r="H177" s="11"/>
       <c r="I177" s="11"/>
       <c r="J177" s="11"/>
       <c r="K177" s="11"/>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A178" s="12"/>
       <c r="B178" s="8"/>
       <c r="C178" s="10"/>
       <c r="D178" s="8"/>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A179" s="12"/>
       <c r="B179" s="8"/>
       <c r="C179" s="10"/>
       <c r="D179" s="8"/>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A180" s="20"/>
-      <c r="B180" s="21"/>
-      <c r="C180" s="22"/>
-      <c r="D180" s="21"/>
-      <c r="E180" s="23"/>
-    </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A181" s="22"/>
-      <c r="B181" s="22"/>
-      <c r="C181" s="22"/>
-      <c r="D181" s="22"/>
-      <c r="E181" s="22"/>
-    </row>
-    <row r="182" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A182" s="21"/>
-      <c r="B182" s="21"/>
-      <c r="C182" s="21"/>
-      <c r="D182" s="21"/>
-      <c r="E182" s="21"/>
-    </row>
-    <row r="183" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A183" s="21"/>
-      <c r="B183" s="21"/>
-      <c r="C183" s="21"/>
-      <c r="D183" s="21"/>
-      <c r="E183" s="21"/>
-    </row>
-    <row r="184" spans="1:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A184" s="21"/>
-      <c r="B184" s="21"/>
-      <c r="C184" s="21"/>
-      <c r="D184" s="21"/>
-      <c r="E184" s="21"/>
-    </row>
-    <row r="185" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A185" s="21"/>
-      <c r="B185" s="21"/>
-      <c r="C185" s="21"/>
-      <c r="D185" s="21"/>
-      <c r="E185" s="21"/>
-    </row>
-    <row r="186" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A186" s="21"/>
-      <c r="B186" s="21"/>
-      <c r="C186" s="21"/>
-      <c r="D186" s="21"/>
-      <c r="E186" s="21"/>
-    </row>
-    <row r="187" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A187" s="21"/>
-      <c r="B187" s="21"/>
-      <c r="C187" s="21"/>
-      <c r="D187" s="21"/>
-      <c r="E187" s="21"/>
-    </row>
-    <row r="188" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A188" s="21"/>
-      <c r="B188" s="21"/>
-      <c r="C188" s="21"/>
-      <c r="D188" s="21"/>
-      <c r="E188" s="21"/>
-    </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A189" s="21"/>
-      <c r="B189" s="21"/>
-      <c r="C189" s="21"/>
-      <c r="D189" s="21"/>
-      <c r="E189" s="21"/>
-    </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A190" s="21"/>
-      <c r="B190" s="21"/>
-      <c r="C190" s="21"/>
-      <c r="D190" s="21"/>
-      <c r="E190" s="21"/>
-    </row>
-    <row r="191" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A191" s="21"/>
-      <c r="B191" s="21"/>
-      <c r="C191" s="21"/>
-      <c r="D191" s="21"/>
-      <c r="E191" s="21"/>
+    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A180" s="16"/>
+      <c r="B180" s="17"/>
+      <c r="C180" s="18"/>
+      <c r="D180" s="17"/>
+      <c r="E180" s="19"/>
+    </row>
+    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A181" s="18"/>
+      <c r="B181" s="18"/>
+      <c r="C181" s="18"/>
+      <c r="D181" s="18"/>
+      <c r="E181" s="18"/>
+    </row>
+    <row r="182" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A182" s="17"/>
+      <c r="B182" s="17"/>
+      <c r="C182" s="17"/>
+      <c r="D182" s="17"/>
+      <c r="E182" s="17"/>
+    </row>
+    <row r="183" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A183" s="17"/>
+      <c r="B183" s="17"/>
+      <c r="C183" s="17"/>
+      <c r="D183" s="17"/>
+      <c r="E183" s="17"/>
+    </row>
+    <row r="184" spans="1:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A184" s="17"/>
+      <c r="B184" s="17"/>
+      <c r="C184" s="17"/>
+      <c r="D184" s="17"/>
+      <c r="E184" s="17"/>
+    </row>
+    <row r="185" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A185" s="17"/>
+      <c r="B185" s="17"/>
+      <c r="C185" s="17"/>
+      <c r="D185" s="17"/>
+      <c r="E185" s="17"/>
+    </row>
+    <row r="186" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A186" s="17"/>
+      <c r="B186" s="17"/>
+      <c r="C186" s="17"/>
+      <c r="D186" s="17"/>
+      <c r="E186" s="17"/>
+    </row>
+    <row r="187" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A187" s="17"/>
+      <c r="B187" s="17"/>
+      <c r="C187" s="17"/>
+      <c r="D187" s="17"/>
+      <c r="E187" s="17"/>
+    </row>
+    <row r="188" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A188" s="17"/>
+      <c r="B188" s="17"/>
+      <c r="C188" s="17"/>
+      <c r="D188" s="17"/>
+      <c r="E188" s="17"/>
+    </row>
+    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A189" s="17"/>
+      <c r="B189" s="17"/>
+      <c r="C189" s="17"/>
+      <c r="D189" s="17"/>
+      <c r="E189" s="17"/>
+    </row>
+    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A190" s="17"/>
+      <c r="B190" s="17"/>
+      <c r="C190" s="17"/>
+      <c r="D190" s="17"/>
+      <c r="E190" s="17"/>
+    </row>
+    <row r="191" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A191" s="17"/>
+      <c r="B191" s="17"/>
+      <c r="C191" s="17"/>
+      <c r="D191" s="17"/>
+      <c r="E191" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="96">
-    <mergeCell ref="A137:A143"/>
-    <mergeCell ref="B137:B143"/>
-    <mergeCell ref="C137:C143"/>
-    <mergeCell ref="B122:B132"/>
-    <mergeCell ref="C122:C132"/>
-    <mergeCell ref="A122:A132"/>
-    <mergeCell ref="B133:B136"/>
-    <mergeCell ref="C133:C136"/>
-    <mergeCell ref="A133:A136"/>
-    <mergeCell ref="A112:A115"/>
-    <mergeCell ref="B112:B115"/>
-    <mergeCell ref="C112:C115"/>
-    <mergeCell ref="B116:B121"/>
-    <mergeCell ref="A116:A121"/>
-    <mergeCell ref="C116:C121"/>
-    <mergeCell ref="C101:C108"/>
-    <mergeCell ref="B101:B108"/>
-    <mergeCell ref="A101:A108"/>
-    <mergeCell ref="B109:B111"/>
-    <mergeCell ref="A109:A111"/>
-    <mergeCell ref="C109:C111"/>
-    <mergeCell ref="B94:B96"/>
-    <mergeCell ref="C94:C96"/>
-    <mergeCell ref="A94:A96"/>
-    <mergeCell ref="A97:A100"/>
-    <mergeCell ref="B97:B100"/>
-    <mergeCell ref="C97:C100"/>
-    <mergeCell ref="C8:C11"/>
-    <mergeCell ref="C3:C7"/>
-    <mergeCell ref="B3:B7"/>
-    <mergeCell ref="A3:A7"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="C12:C15"/>
-    <mergeCell ref="B12:B15"/>
-    <mergeCell ref="A12:A15"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="B16:B18"/>
-    <mergeCell ref="A16:A18"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="A20:A22"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="B32:B34"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="C36:C38"/>
-    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="C90:C93"/>
+    <mergeCell ref="B90:B93"/>
+    <mergeCell ref="A90:A93"/>
+    <mergeCell ref="C80:C83"/>
+    <mergeCell ref="B80:B83"/>
+    <mergeCell ref="A80:A83"/>
+    <mergeCell ref="C84:C87"/>
+    <mergeCell ref="B84:B87"/>
+    <mergeCell ref="A84:A87"/>
+    <mergeCell ref="C71:C74"/>
+    <mergeCell ref="B71:B74"/>
+    <mergeCell ref="A71:A74"/>
+    <mergeCell ref="C75:C78"/>
+    <mergeCell ref="B75:B78"/>
+    <mergeCell ref="A75:A78"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="C59:C62"/>
+    <mergeCell ref="B59:B62"/>
+    <mergeCell ref="A59:A62"/>
+    <mergeCell ref="C53:C57"/>
+    <mergeCell ref="B53:B57"/>
+    <mergeCell ref="A53:A57"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="C49:C52"/>
+    <mergeCell ref="B49:B52"/>
+    <mergeCell ref="A49:A52"/>
     <mergeCell ref="C44:C46"/>
     <mergeCell ref="B44:B46"/>
     <mergeCell ref="A44:A46"/>
@@ -3749,39 +3844,59 @@
     <mergeCell ref="C42:C43"/>
     <mergeCell ref="B42:B43"/>
     <mergeCell ref="A42:A43"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="C49:C52"/>
-    <mergeCell ref="B49:B52"/>
-    <mergeCell ref="A49:A52"/>
-    <mergeCell ref="C59:C62"/>
-    <mergeCell ref="B59:B62"/>
-    <mergeCell ref="A59:A62"/>
-    <mergeCell ref="C53:C57"/>
-    <mergeCell ref="B53:B57"/>
-    <mergeCell ref="A53:A57"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="C71:C74"/>
-    <mergeCell ref="B71:B74"/>
-    <mergeCell ref="A71:A74"/>
-    <mergeCell ref="C75:C78"/>
-    <mergeCell ref="B75:B78"/>
-    <mergeCell ref="A75:A78"/>
-    <mergeCell ref="C90:C93"/>
-    <mergeCell ref="B90:B93"/>
-    <mergeCell ref="A90:A93"/>
-    <mergeCell ref="C80:C83"/>
-    <mergeCell ref="B80:B83"/>
-    <mergeCell ref="A80:A83"/>
-    <mergeCell ref="C84:C87"/>
-    <mergeCell ref="B84:B87"/>
-    <mergeCell ref="A84:A87"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="B32:B34"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="C12:C15"/>
+    <mergeCell ref="B12:B15"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="C8:C11"/>
+    <mergeCell ref="C3:C7"/>
+    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="B94:B96"/>
+    <mergeCell ref="C94:C96"/>
+    <mergeCell ref="A94:A96"/>
+    <mergeCell ref="A97:A100"/>
+    <mergeCell ref="B97:B100"/>
+    <mergeCell ref="C97:C100"/>
+    <mergeCell ref="C101:C108"/>
+    <mergeCell ref="B101:B108"/>
+    <mergeCell ref="A101:A108"/>
+    <mergeCell ref="B109:B111"/>
+    <mergeCell ref="A109:A111"/>
+    <mergeCell ref="C109:C111"/>
+    <mergeCell ref="A112:A115"/>
+    <mergeCell ref="B112:B115"/>
+    <mergeCell ref="C112:C115"/>
+    <mergeCell ref="B116:B121"/>
+    <mergeCell ref="A116:A121"/>
+    <mergeCell ref="C116:C121"/>
+    <mergeCell ref="A137:A143"/>
+    <mergeCell ref="B137:B143"/>
+    <mergeCell ref="C137:C143"/>
+    <mergeCell ref="B122:B132"/>
+    <mergeCell ref="C122:C132"/>
+    <mergeCell ref="A122:A132"/>
+    <mergeCell ref="B133:B136"/>
+    <mergeCell ref="C133:C136"/>
+    <mergeCell ref="A133:A136"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/thesis/tables/algoritma_kullanım_listesi.xlsx
+++ b/thesis/tables/algoritma_kullanım_listesi.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\URL-Phishing-Detection\thesis\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{563621FC-ABD3-4D54-A1C1-5BAAAEAB778B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DBCC748-EE08-4E1A-AFBE-B79E79AB2381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sayfa1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="277">
   <si>
     <t>Random Forest,</t>
   </si>
@@ -1083,12 +1084,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="5">
@@ -1155,7 +1162,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1260,6 +1267,33 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1586,13 +1620,13 @@
       </c>
     </row>
     <row r="3" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="38" t="s">
         <v>178</v>
       </c>
-      <c r="B3" s="29">
+      <c r="B3" s="38">
         <v>2019</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="38" t="s">
         <v>24</v>
       </c>
       <c r="D3" s="5" t="s">
@@ -1603,9 +1637,9 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="29"/>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
+      <c r="A4" s="38"/>
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
       <c r="D4" s="5" t="s">
         <v>1</v>
       </c>
@@ -1614,9 +1648,9 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="29"/>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
+      <c r="A5" s="38"/>
+      <c r="B5" s="38"/>
+      <c r="C5" s="38"/>
       <c r="D5" s="5" t="s">
         <v>2</v>
       </c>
@@ -1625,9 +1659,9 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="29"/>
-      <c r="B6" s="29"/>
-      <c r="C6" s="29"/>
+      <c r="A6" s="38"/>
+      <c r="B6" s="38"/>
+      <c r="C6" s="38"/>
       <c r="D6" s="5" t="s">
         <v>3</v>
       </c>
@@ -1636,9 +1670,9 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="29"/>
-      <c r="B7" s="29"/>
-      <c r="C7" s="29"/>
+      <c r="A7" s="38"/>
+      <c r="B7" s="38"/>
+      <c r="C7" s="38"/>
       <c r="D7" s="5" t="s">
         <v>4</v>
       </c>
@@ -1647,13 +1681,13 @@
       </c>
     </row>
     <row r="8" spans="1:5" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="41" t="s">
         <v>179</v>
       </c>
-      <c r="B8" s="29">
+      <c r="B8" s="41">
         <v>2023</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C8" s="38" t="s">
         <v>24</v>
       </c>
       <c r="D8" s="5" t="s">
@@ -1664,9 +1698,9 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="29"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="29"/>
+      <c r="A9" s="41"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="38"/>
       <c r="D9" s="3" t="s">
         <v>0</v>
       </c>
@@ -1675,9 +1709,9 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="29"/>
-      <c r="B10" s="29"/>
-      <c r="C10" s="29"/>
+      <c r="A10" s="41"/>
+      <c r="B10" s="41"/>
+      <c r="C10" s="38"/>
       <c r="D10" s="5" t="s">
         <v>28</v>
       </c>
@@ -1686,9 +1720,9 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="29"/>
-      <c r="B11" s="29"/>
-      <c r="C11" s="29"/>
+      <c r="A11" s="41"/>
+      <c r="B11" s="41"/>
+      <c r="C11" s="38"/>
       <c r="D11" s="5" t="s">
         <v>29</v>
       </c>
@@ -1697,13 +1731,13 @@
       </c>
     </row>
     <row r="12" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="29" t="s">
+      <c r="A12" s="41" t="s">
         <v>180</v>
       </c>
-      <c r="B12" s="29">
+      <c r="B12" s="41">
         <v>2022</v>
       </c>
-      <c r="C12" s="29" t="s">
+      <c r="C12" s="38" t="s">
         <v>24</v>
       </c>
       <c r="D12" s="5" t="s">
@@ -1714,9 +1748,9 @@
       </c>
     </row>
     <row r="13" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="29"/>
-      <c r="B13" s="29"/>
-      <c r="C13" s="29"/>
+      <c r="A13" s="41"/>
+      <c r="B13" s="41"/>
+      <c r="C13" s="38"/>
       <c r="D13" s="5" t="s">
         <v>35</v>
       </c>
@@ -1725,9 +1759,9 @@
       </c>
     </row>
     <row r="14" spans="1:5" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="29"/>
-      <c r="B14" s="29"/>
-      <c r="C14" s="29"/>
+      <c r="A14" s="41"/>
+      <c r="B14" s="41"/>
+      <c r="C14" s="38"/>
       <c r="D14" s="5" t="s">
         <v>36</v>
       </c>
@@ -1736,9 +1770,9 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="29"/>
-      <c r="B15" s="29"/>
-      <c r="C15" s="29"/>
+      <c r="A15" s="41"/>
+      <c r="B15" s="41"/>
+      <c r="C15" s="38"/>
       <c r="D15" s="5" t="s">
         <v>15</v>
       </c>
@@ -1747,13 +1781,13 @@
       </c>
     </row>
     <row r="16" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="29" t="s">
+      <c r="A16" s="38" t="s">
         <v>181</v>
       </c>
-      <c r="B16" s="29">
+      <c r="B16" s="38">
         <v>2021</v>
       </c>
-      <c r="C16" s="29" t="s">
+      <c r="C16" s="38" t="s">
         <v>24</v>
       </c>
       <c r="D16" s="5" t="s">
@@ -1764,9 +1798,9 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="29"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="29"/>
+      <c r="A17" s="38"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="38"/>
       <c r="D17" s="3" t="s">
         <v>42</v>
       </c>
@@ -1775,9 +1809,9 @@
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="29"/>
-      <c r="B18" s="29"/>
-      <c r="C18" s="29"/>
+      <c r="A18" s="38"/>
+      <c r="B18" s="38"/>
+      <c r="C18" s="38"/>
       <c r="D18" s="3" t="s">
         <v>43</v>
       </c>
@@ -1803,13 +1837,13 @@
       </c>
     </row>
     <row r="20" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="29" t="s">
+      <c r="A20" s="38" t="s">
         <v>183</v>
       </c>
-      <c r="B20" s="30">
+      <c r="B20" s="37">
         <v>2023</v>
       </c>
-      <c r="C20" s="31" t="s">
+      <c r="C20" s="39" t="s">
         <v>50</v>
       </c>
       <c r="D20" s="3" t="s">
@@ -1820,9 +1854,9 @@
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="32"/>
-      <c r="B21" s="30"/>
-      <c r="C21" s="31"/>
+      <c r="A21" s="40"/>
+      <c r="B21" s="37"/>
+      <c r="C21" s="39"/>
       <c r="D21" s="3" t="s">
         <v>51</v>
       </c>
@@ -1831,9 +1865,9 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="32"/>
-      <c r="B22" s="30"/>
-      <c r="C22" s="31"/>
+      <c r="A22" s="40"/>
+      <c r="B22" s="37"/>
+      <c r="C22" s="39"/>
       <c r="D22" s="3" t="s">
         <v>52</v>
       </c>
@@ -1842,13 +1876,13 @@
       </c>
     </row>
     <row r="23" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="29" t="s">
+      <c r="A23" s="38" t="s">
         <v>184</v>
       </c>
-      <c r="B23" s="30">
+      <c r="B23" s="37">
         <v>2020</v>
       </c>
-      <c r="C23" s="31" t="s">
+      <c r="C23" s="39" t="s">
         <v>24</v>
       </c>
       <c r="D23" s="3" t="s">
@@ -1859,9 +1893,9 @@
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="32"/>
-      <c r="B24" s="30"/>
-      <c r="C24" s="31"/>
+      <c r="A24" s="40"/>
+      <c r="B24" s="37"/>
+      <c r="C24" s="39"/>
       <c r="D24" s="3" t="s">
         <v>22</v>
       </c>
@@ -1870,13 +1904,13 @@
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="29" t="s">
+      <c r="A25" s="38" t="s">
         <v>185</v>
       </c>
-      <c r="B25" s="30">
+      <c r="B25" s="37">
         <v>2019</v>
       </c>
-      <c r="C25" s="30" t="s">
+      <c r="C25" s="37" t="s">
         <v>58</v>
       </c>
       <c r="D25" s="3" t="s">
@@ -1887,9 +1921,9 @@
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="32"/>
-      <c r="B26" s="30"/>
-      <c r="C26" s="30"/>
+      <c r="A26" s="40"/>
+      <c r="B26" s="37"/>
+      <c r="C26" s="37"/>
       <c r="D26" s="3" t="s">
         <v>22</v>
       </c>
@@ -1983,13 +2017,13 @@
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="29" t="s">
+      <c r="A32" s="38" t="s">
         <v>191</v>
       </c>
-      <c r="B32" s="30">
+      <c r="B32" s="37">
         <v>2023</v>
       </c>
-      <c r="C32" s="30" t="s">
+      <c r="C32" s="37" t="s">
         <v>20</v>
       </c>
       <c r="D32" s="3" t="s">
@@ -2000,9 +2034,9 @@
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="32"/>
-      <c r="B33" s="30"/>
-      <c r="C33" s="30"/>
+      <c r="A33" s="40"/>
+      <c r="B33" s="37"/>
+      <c r="C33" s="37"/>
       <c r="D33" s="3" t="s">
         <v>1</v>
       </c>
@@ -2011,9 +2045,9 @@
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="32"/>
-      <c r="B34" s="30"/>
-      <c r="C34" s="30"/>
+      <c r="A34" s="40"/>
+      <c r="B34" s="37"/>
+      <c r="C34" s="37"/>
       <c r="D34" s="3" t="s">
         <v>52</v>
       </c>
@@ -2039,13 +2073,13 @@
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="29" t="s">
+      <c r="A36" s="41" t="s">
         <v>193</v>
       </c>
-      <c r="B36" s="30">
+      <c r="B36" s="42">
         <v>2022</v>
       </c>
-      <c r="C36" s="30" t="s">
+      <c r="C36" s="37" t="s">
         <v>82</v>
       </c>
       <c r="D36" s="3" t="s">
@@ -2056,9 +2090,9 @@
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="32"/>
-      <c r="B37" s="30"/>
-      <c r="C37" s="30"/>
+      <c r="A37" s="43"/>
+      <c r="B37" s="42"/>
+      <c r="C37" s="37"/>
       <c r="D37" s="3" t="s">
         <v>83</v>
       </c>
@@ -2067,9 +2101,9 @@
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="32"/>
-      <c r="B38" s="30"/>
-      <c r="C38" s="30"/>
+      <c r="A38" s="43"/>
+      <c r="B38" s="42"/>
+      <c r="C38" s="37"/>
       <c r="D38" s="3" t="s">
         <v>21</v>
       </c>
@@ -2095,13 +2129,13 @@
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="29" t="s">
+      <c r="A40" s="38" t="s">
         <v>195</v>
       </c>
-      <c r="B40" s="30">
+      <c r="B40" s="37">
         <v>2021</v>
       </c>
-      <c r="C40" s="30" t="s">
+      <c r="C40" s="37" t="s">
         <v>89</v>
       </c>
       <c r="D40" s="3" t="s">
@@ -2112,9 +2146,9 @@
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="32"/>
-      <c r="B41" s="30"/>
-      <c r="C41" s="30"/>
+      <c r="A41" s="40"/>
+      <c r="B41" s="37"/>
+      <c r="C41" s="37"/>
       <c r="D41" s="3" t="s">
         <v>176</v>
       </c>
@@ -2123,13 +2157,13 @@
       </c>
     </row>
     <row r="42" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="29" t="s">
+      <c r="A42" s="38" t="s">
         <v>196</v>
       </c>
-      <c r="B42" s="30">
+      <c r="B42" s="37">
         <v>2020</v>
       </c>
-      <c r="C42" s="31" t="s">
+      <c r="C42" s="39" t="s">
         <v>90</v>
       </c>
       <c r="D42" s="3" t="s">
@@ -2140,9 +2174,9 @@
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="32"/>
-      <c r="B43" s="30"/>
-      <c r="C43" s="31"/>
+      <c r="A43" s="40"/>
+      <c r="B43" s="37"/>
+      <c r="C43" s="39"/>
       <c r="D43" s="3" t="s">
         <v>91</v>
       </c>
@@ -2151,13 +2185,13 @@
       </c>
     </row>
     <row r="44" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="29" t="s">
+      <c r="A44" s="38" t="s">
         <v>197</v>
       </c>
-      <c r="B44" s="30">
+      <c r="B44" s="37">
         <v>2020</v>
       </c>
-      <c r="C44" s="31" t="s">
+      <c r="C44" s="39" t="s">
         <v>24</v>
       </c>
       <c r="D44" s="3" t="s">
@@ -2168,9 +2202,9 @@
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="32"/>
-      <c r="B45" s="30"/>
-      <c r="C45" s="31"/>
+      <c r="A45" s="40"/>
+      <c r="B45" s="37"/>
+      <c r="C45" s="39"/>
       <c r="D45" s="3" t="s">
         <v>96</v>
       </c>
@@ -2179,9 +2213,9 @@
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="32"/>
-      <c r="B46" s="30"/>
-      <c r="C46" s="31"/>
+      <c r="A46" s="40"/>
+      <c r="B46" s="37"/>
+      <c r="C46" s="39"/>
       <c r="D46" s="3" t="s">
         <v>97</v>
       </c>
@@ -2190,13 +2224,13 @@
       </c>
     </row>
     <row r="47" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="29" t="s">
+      <c r="A47" s="38" t="s">
         <v>198</v>
       </c>
-      <c r="B47" s="30">
+      <c r="B47" s="37">
         <v>2022</v>
       </c>
-      <c r="C47" s="31" t="s">
+      <c r="C47" s="39" t="s">
         <v>101</v>
       </c>
       <c r="D47" s="3" t="s">
@@ -2207,9 +2241,9 @@
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="32"/>
-      <c r="B48" s="30"/>
-      <c r="C48" s="31"/>
+      <c r="A48" s="40"/>
+      <c r="B48" s="37"/>
+      <c r="C48" s="39"/>
       <c r="D48" s="3" t="s">
         <v>102</v>
       </c>
@@ -2218,13 +2252,13 @@
       </c>
     </row>
     <row r="49" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="29" t="s">
+      <c r="A49" s="38" t="s">
         <v>199</v>
       </c>
-      <c r="B49" s="30">
+      <c r="B49" s="37">
         <v>2017</v>
       </c>
-      <c r="C49" s="31" t="s">
+      <c r="C49" s="39" t="s">
         <v>101</v>
       </c>
       <c r="D49" s="3" t="s">
@@ -2235,9 +2269,9 @@
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="32"/>
-      <c r="B50" s="30"/>
-      <c r="C50" s="31"/>
+      <c r="A50" s="40"/>
+      <c r="B50" s="37"/>
+      <c r="C50" s="39"/>
       <c r="D50" s="3" t="s">
         <v>218</v>
       </c>
@@ -2246,9 +2280,9 @@
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="32"/>
-      <c r="B51" s="30"/>
-      <c r="C51" s="31"/>
+      <c r="A51" s="40"/>
+      <c r="B51" s="37"/>
+      <c r="C51" s="39"/>
       <c r="D51" s="3" t="s">
         <v>28</v>
       </c>
@@ -2257,9 +2291,9 @@
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="32"/>
-      <c r="B52" s="30"/>
-      <c r="C52" s="31"/>
+      <c r="A52" s="40"/>
+      <c r="B52" s="37"/>
+      <c r="C52" s="39"/>
       <c r="D52" s="3" t="s">
         <v>22</v>
       </c>
@@ -2268,13 +2302,13 @@
       </c>
     </row>
     <row r="53" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="29" t="s">
+      <c r="A53" s="38" t="s">
         <v>200</v>
       </c>
-      <c r="B53" s="30">
+      <c r="B53" s="37">
         <v>2022</v>
       </c>
-      <c r="C53" s="31" t="s">
+      <c r="C53" s="39" t="s">
         <v>101</v>
       </c>
       <c r="D53" s="3" t="s">
@@ -2285,9 +2319,9 @@
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="32"/>
-      <c r="B54" s="30"/>
-      <c r="C54" s="31"/>
+      <c r="A54" s="40"/>
+      <c r="B54" s="37"/>
+      <c r="C54" s="39"/>
       <c r="D54" s="3" t="s">
         <v>25</v>
       </c>
@@ -2296,9 +2330,9 @@
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="32"/>
-      <c r="B55" s="30"/>
-      <c r="C55" s="31"/>
+      <c r="A55" s="40"/>
+      <c r="B55" s="37"/>
+      <c r="C55" s="39"/>
       <c r="D55" s="3" t="s">
         <v>94</v>
       </c>
@@ -2307,9 +2341,9 @@
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="32"/>
-      <c r="B56" s="30"/>
-      <c r="C56" s="31"/>
+      <c r="A56" s="40"/>
+      <c r="B56" s="37"/>
+      <c r="C56" s="39"/>
       <c r="D56" s="3" t="s">
         <v>1</v>
       </c>
@@ -2318,9 +2352,9 @@
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="32"/>
-      <c r="B57" s="30"/>
-      <c r="C57" s="31"/>
+      <c r="A57" s="40"/>
+      <c r="B57" s="37"/>
+      <c r="C57" s="39"/>
       <c r="D57" s="3" t="s">
         <v>26</v>
       </c>
@@ -2346,13 +2380,13 @@
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="29" t="s">
+      <c r="A59" s="38" t="s">
         <v>202</v>
       </c>
-      <c r="B59" s="30">
+      <c r="B59" s="37">
         <v>2022</v>
       </c>
-      <c r="C59" s="30" t="s">
+      <c r="C59" s="37" t="s">
         <v>67</v>
       </c>
       <c r="D59" s="3" t="s">
@@ -2363,9 +2397,9 @@
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="32"/>
-      <c r="B60" s="30"/>
-      <c r="C60" s="30"/>
+      <c r="A60" s="40"/>
+      <c r="B60" s="37"/>
+      <c r="C60" s="37"/>
       <c r="D60" s="3" t="s">
         <v>25</v>
       </c>
@@ -2374,9 +2408,9 @@
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="32"/>
-      <c r="B61" s="30"/>
-      <c r="C61" s="30"/>
+      <c r="A61" s="40"/>
+      <c r="B61" s="37"/>
+      <c r="C61" s="37"/>
       <c r="D61" s="3" t="s">
         <v>68</v>
       </c>
@@ -2385,9 +2419,9 @@
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="32"/>
-      <c r="B62" s="30"/>
-      <c r="C62" s="30"/>
+      <c r="A62" s="40"/>
+      <c r="B62" s="37"/>
+      <c r="C62" s="37"/>
       <c r="D62" s="3" t="s">
         <v>69</v>
       </c>
@@ -2447,13 +2481,13 @@
       </c>
     </row>
     <row r="66" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="29" t="s">
+      <c r="A66" s="38" t="s">
         <v>206</v>
       </c>
-      <c r="B66" s="30">
+      <c r="B66" s="37">
         <v>2012</v>
       </c>
-      <c r="C66" s="31" t="s">
+      <c r="C66" s="39" t="s">
         <v>127</v>
       </c>
       <c r="D66" s="3" t="s">
@@ -2464,9 +2498,9 @@
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="32"/>
-      <c r="B67" s="30"/>
-      <c r="C67" s="31"/>
+      <c r="A67" s="40"/>
+      <c r="B67" s="37"/>
+      <c r="C67" s="39"/>
       <c r="D67" s="3" t="s">
         <v>128</v>
       </c>
@@ -2475,13 +2509,13 @@
       </c>
     </row>
     <row r="68" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="29" t="s">
+      <c r="A68" s="38" t="s">
         <v>207</v>
       </c>
-      <c r="B68" s="30">
+      <c r="B68" s="37">
         <v>2022</v>
       </c>
-      <c r="C68" s="31" t="s">
+      <c r="C68" s="39" t="s">
         <v>24</v>
       </c>
       <c r="D68" s="3" t="s">
@@ -2492,9 +2526,9 @@
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="32"/>
-      <c r="B69" s="30"/>
-      <c r="C69" s="31"/>
+      <c r="A69" s="40"/>
+      <c r="B69" s="37"/>
+      <c r="C69" s="39"/>
       <c r="D69" s="3" t="s">
         <v>113</v>
       </c>
@@ -2520,13 +2554,13 @@
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="29" t="s">
+      <c r="A71" s="38" t="s">
         <v>209</v>
       </c>
-      <c r="B71" s="30">
+      <c r="B71" s="37">
         <v>2020</v>
       </c>
-      <c r="C71" s="30" t="s">
+      <c r="C71" s="37" t="s">
         <v>73</v>
       </c>
       <c r="D71" s="3" t="s">
@@ -2537,9 +2571,9 @@
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="32"/>
-      <c r="B72" s="30"/>
-      <c r="C72" s="30"/>
+      <c r="A72" s="40"/>
+      <c r="B72" s="37"/>
+      <c r="C72" s="37"/>
       <c r="D72" s="3" t="s">
         <v>141</v>
       </c>
@@ -2548,9 +2582,9 @@
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="32"/>
-      <c r="B73" s="30"/>
-      <c r="C73" s="30"/>
+      <c r="A73" s="40"/>
+      <c r="B73" s="37"/>
+      <c r="C73" s="37"/>
       <c r="D73" s="3" t="s">
         <v>142</v>
       </c>
@@ -2559,9 +2593,9 @@
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="32"/>
-      <c r="B74" s="30"/>
-      <c r="C74" s="30"/>
+      <c r="A74" s="40"/>
+      <c r="B74" s="37"/>
+      <c r="C74" s="37"/>
       <c r="D74" s="3" t="s">
         <v>139</v>
       </c>
@@ -2570,13 +2604,13 @@
       </c>
     </row>
     <row r="75" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="29" t="s">
+      <c r="A75" s="38" t="s">
         <v>210</v>
       </c>
-      <c r="B75" s="30">
+      <c r="B75" s="37">
         <v>2021</v>
       </c>
-      <c r="C75" s="31" t="s">
+      <c r="C75" s="39" t="s">
         <v>138</v>
       </c>
       <c r="D75" s="3" t="s">
@@ -2587,9 +2621,9 @@
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" s="32"/>
-      <c r="B76" s="30"/>
-      <c r="C76" s="31"/>
+      <c r="A76" s="40"/>
+      <c r="B76" s="37"/>
+      <c r="C76" s="39"/>
       <c r="D76" s="3" t="s">
         <v>143</v>
       </c>
@@ -2598,9 +2632,9 @@
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="32"/>
-      <c r="B77" s="30"/>
-      <c r="C77" s="31"/>
+      <c r="A77" s="40"/>
+      <c r="B77" s="37"/>
+      <c r="C77" s="39"/>
       <c r="D77" s="3" t="s">
         <v>147</v>
       </c>
@@ -2609,9 +2643,9 @@
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="32"/>
-      <c r="B78" s="30"/>
-      <c r="C78" s="31"/>
+      <c r="A78" s="40"/>
+      <c r="B78" s="37"/>
+      <c r="C78" s="39"/>
       <c r="D78" s="3" t="s">
         <v>148</v>
       </c>
@@ -2637,13 +2671,13 @@
       </c>
     </row>
     <row r="80" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="29" t="s">
+      <c r="A80" s="38" t="s">
         <v>212</v>
       </c>
-      <c r="B80" s="30">
+      <c r="B80" s="37">
         <v>2018</v>
       </c>
-      <c r="C80" s="31" t="s">
+      <c r="C80" s="39" t="s">
         <v>152</v>
       </c>
       <c r="D80" s="3" t="s">
@@ -2654,9 +2688,9 @@
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="32"/>
-      <c r="B81" s="30"/>
-      <c r="C81" s="31"/>
+      <c r="A81" s="40"/>
+      <c r="B81" s="37"/>
+      <c r="C81" s="39"/>
       <c r="D81" s="3" t="s">
         <v>153</v>
       </c>
@@ -2665,9 +2699,9 @@
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="32"/>
-      <c r="B82" s="30"/>
-      <c r="C82" s="31"/>
+      <c r="A82" s="40"/>
+      <c r="B82" s="37"/>
+      <c r="C82" s="39"/>
       <c r="D82" s="3" t="s">
         <v>154</v>
       </c>
@@ -2676,9 +2710,9 @@
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="32"/>
-      <c r="B83" s="30"/>
-      <c r="C83" s="31"/>
+      <c r="A83" s="40"/>
+      <c r="B83" s="37"/>
+      <c r="C83" s="39"/>
       <c r="D83" s="3" t="s">
         <v>17</v>
       </c>
@@ -2687,13 +2721,13 @@
       </c>
     </row>
     <row r="84" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="29" t="s">
+      <c r="A84" s="38" t="s">
         <v>213</v>
       </c>
-      <c r="B84" s="30">
+      <c r="B84" s="37">
         <v>2017</v>
       </c>
-      <c r="C84" s="31" t="s">
+      <c r="C84" s="39" t="s">
         <v>159</v>
       </c>
       <c r="D84" s="3" t="s">
@@ -2704,9 +2738,9 @@
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" s="32"/>
-      <c r="B85" s="30"/>
-      <c r="C85" s="31"/>
+      <c r="A85" s="40"/>
+      <c r="B85" s="37"/>
+      <c r="C85" s="39"/>
       <c r="D85" s="3" t="s">
         <v>160</v>
       </c>
@@ -2715,9 +2749,9 @@
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" s="32"/>
-      <c r="B86" s="30"/>
-      <c r="C86" s="31"/>
+      <c r="A86" s="40"/>
+      <c r="B86" s="37"/>
+      <c r="C86" s="39"/>
       <c r="D86" s="3" t="s">
         <v>25</v>
       </c>
@@ -2726,9 +2760,9 @@
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" s="32"/>
-      <c r="B87" s="30"/>
-      <c r="C87" s="31"/>
+      <c r="A87" s="40"/>
+      <c r="B87" s="37"/>
+      <c r="C87" s="39"/>
       <c r="D87" s="3" t="s">
         <v>161</v>
       </c>
@@ -2771,13 +2805,13 @@
       </c>
     </row>
     <row r="90" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="29" t="s">
+      <c r="A90" s="38" t="s">
         <v>216</v>
       </c>
-      <c r="B90" s="30">
+      <c r="B90" s="37">
         <v>2020</v>
       </c>
-      <c r="C90" s="30" t="s">
+      <c r="C90" s="37" t="s">
         <v>119</v>
       </c>
       <c r="D90" s="3" t="s">
@@ -2788,9 +2822,9 @@
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" s="29"/>
-      <c r="B91" s="30"/>
-      <c r="C91" s="30"/>
+      <c r="A91" s="38"/>
+      <c r="B91" s="37"/>
+      <c r="C91" s="37"/>
       <c r="D91" s="3" t="s">
         <v>25</v>
       </c>
@@ -2799,9 +2833,9 @@
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" s="29"/>
-      <c r="B92" s="30"/>
-      <c r="C92" s="30"/>
+      <c r="A92" s="38"/>
+      <c r="B92" s="37"/>
+      <c r="C92" s="37"/>
       <c r="D92" s="3" t="s">
         <v>34</v>
       </c>
@@ -2810,9 +2844,9 @@
       </c>
     </row>
     <row r="93" spans="1:5" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="29"/>
-      <c r="B93" s="30"/>
-      <c r="C93" s="30"/>
+      <c r="A93" s="38"/>
+      <c r="B93" s="37"/>
+      <c r="C93" s="37"/>
       <c r="D93" s="3" t="s">
         <v>172</v>
       </c>
@@ -2821,13 +2855,13 @@
       </c>
     </row>
     <row r="94" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="29" t="s">
+      <c r="A94" s="38" t="s">
         <v>224</v>
       </c>
-      <c r="B94" s="30">
+      <c r="B94" s="37">
         <v>2024</v>
       </c>
-      <c r="C94" s="30" t="s">
+      <c r="C94" s="37" t="s">
         <v>223</v>
       </c>
       <c r="D94" s="3" t="s">
@@ -2838,9 +2872,9 @@
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" s="29"/>
-      <c r="B95" s="30"/>
-      <c r="C95" s="30"/>
+      <c r="A95" s="38"/>
+      <c r="B95" s="37"/>
+      <c r="C95" s="37"/>
       <c r="D95" s="3" t="s">
         <v>219</v>
       </c>
@@ -2849,9 +2883,9 @@
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" s="29"/>
-      <c r="B96" s="30"/>
-      <c r="C96" s="30"/>
+      <c r="A96" s="38"/>
+      <c r="B96" s="37"/>
+      <c r="C96" s="37"/>
       <c r="D96" s="3" t="s">
         <v>4</v>
       </c>
@@ -2860,13 +2894,13 @@
       </c>
     </row>
     <row r="97" spans="1:5" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="29" t="s">
+      <c r="A97" s="38" t="s">
         <v>230</v>
       </c>
-      <c r="B97" s="30">
+      <c r="B97" s="37">
         <v>2024</v>
       </c>
-      <c r="C97" s="31" t="s">
+      <c r="C97" s="39" t="s">
         <v>231</v>
       </c>
       <c r="D97" s="3" t="s">
@@ -2877,9 +2911,9 @@
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="29"/>
-      <c r="B98" s="30"/>
-      <c r="C98" s="30"/>
+      <c r="A98" s="38"/>
+      <c r="B98" s="37"/>
+      <c r="C98" s="37"/>
       <c r="D98" s="3" t="s">
         <v>4</v>
       </c>
@@ -2888,9 +2922,9 @@
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="29"/>
-      <c r="B99" s="30"/>
-      <c r="C99" s="30"/>
+      <c r="A99" s="38"/>
+      <c r="B99" s="37"/>
+      <c r="C99" s="37"/>
       <c r="D99" s="3" t="s">
         <v>17</v>
       </c>
@@ -2899,9 +2933,9 @@
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" s="29"/>
-      <c r="B100" s="30"/>
-      <c r="C100" s="30"/>
+      <c r="A100" s="38"/>
+      <c r="B100" s="37"/>
+      <c r="C100" s="37"/>
       <c r="D100" s="3" t="s">
         <v>18</v>
       </c>
@@ -2910,13 +2944,13 @@
       </c>
     </row>
     <row r="101" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="29" t="s">
+      <c r="A101" s="38" t="s">
         <v>232</v>
       </c>
-      <c r="B101" s="30">
+      <c r="B101" s="37">
         <v>2024</v>
       </c>
-      <c r="C101" s="30" t="s">
+      <c r="C101" s="37" t="s">
         <v>233</v>
       </c>
       <c r="D101" s="3" t="s">
@@ -2927,9 +2961,9 @@
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" s="29"/>
-      <c r="B102" s="30"/>
-      <c r="C102" s="30"/>
+      <c r="A102" s="38"/>
+      <c r="B102" s="37"/>
+      <c r="C102" s="37"/>
       <c r="D102" s="3" t="s">
         <v>176</v>
       </c>
@@ -2938,9 +2972,9 @@
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A103" s="29"/>
-      <c r="B103" s="30"/>
-      <c r="C103" s="30"/>
+      <c r="A103" s="38"/>
+      <c r="B103" s="37"/>
+      <c r="C103" s="37"/>
       <c r="D103" s="3" t="s">
         <v>17</v>
       </c>
@@ -2949,9 +2983,9 @@
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A104" s="29"/>
-      <c r="B104" s="30"/>
-      <c r="C104" s="30"/>
+      <c r="A104" s="38"/>
+      <c r="B104" s="37"/>
+      <c r="C104" s="37"/>
       <c r="D104" s="3" t="s">
         <v>52</v>
       </c>
@@ -2960,9 +2994,9 @@
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105" s="29"/>
-      <c r="B105" s="30"/>
-      <c r="C105" s="30"/>
+      <c r="A105" s="38"/>
+      <c r="B105" s="37"/>
+      <c r="C105" s="37"/>
       <c r="D105" s="3" t="s">
         <v>4</v>
       </c>
@@ -2971,9 +3005,9 @@
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A106" s="29"/>
-      <c r="B106" s="30"/>
-      <c r="C106" s="30"/>
+      <c r="A106" s="38"/>
+      <c r="B106" s="37"/>
+      <c r="C106" s="37"/>
       <c r="D106" s="3" t="s">
         <v>225</v>
       </c>
@@ -2982,9 +3016,9 @@
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A107" s="29"/>
-      <c r="B107" s="30"/>
-      <c r="C107" s="30"/>
+      <c r="A107" s="38"/>
+      <c r="B107" s="37"/>
+      <c r="C107" s="37"/>
       <c r="D107" s="3" t="s">
         <v>234</v>
       </c>
@@ -2993,9 +3027,9 @@
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A108" s="29"/>
-      <c r="B108" s="30"/>
-      <c r="C108" s="30"/>
+      <c r="A108" s="38"/>
+      <c r="B108" s="37"/>
+      <c r="C108" s="37"/>
       <c r="D108" s="3" t="s">
         <v>235</v>
       </c>
@@ -3004,13 +3038,13 @@
       </c>
     </row>
     <row r="109" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="29" t="s">
+      <c r="A109" s="41" t="s">
         <v>244</v>
       </c>
-      <c r="B109" s="30">
+      <c r="B109" s="42">
         <v>2024</v>
       </c>
-      <c r="C109" s="31" t="s">
+      <c r="C109" s="39" t="s">
         <v>231</v>
       </c>
       <c r="D109" s="3" t="s">
@@ -3021,9 +3055,9 @@
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A110" s="29"/>
-      <c r="B110" s="30"/>
-      <c r="C110" s="30"/>
+      <c r="A110" s="41"/>
+      <c r="B110" s="42"/>
+      <c r="C110" s="37"/>
       <c r="D110" s="3" t="s">
         <v>15</v>
       </c>
@@ -3032,9 +3066,9 @@
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111" s="29"/>
-      <c r="B111" s="30"/>
-      <c r="C111" s="30"/>
+      <c r="A111" s="41"/>
+      <c r="B111" s="42"/>
+      <c r="C111" s="37"/>
       <c r="D111" s="3" t="s">
         <v>245</v>
       </c>
@@ -3043,13 +3077,13 @@
       </c>
     </row>
     <row r="112" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="29" t="s">
+      <c r="A112" s="38" t="s">
         <v>250</v>
       </c>
-      <c r="B112" s="30">
+      <c r="B112" s="37">
         <v>2025</v>
       </c>
-      <c r="C112" s="30"/>
+      <c r="C112" s="37"/>
       <c r="D112" s="3" t="s">
         <v>246</v>
       </c>
@@ -3058,9 +3092,9 @@
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A113" s="29"/>
-      <c r="B113" s="30"/>
-      <c r="C113" s="30"/>
+      <c r="A113" s="38"/>
+      <c r="B113" s="37"/>
+      <c r="C113" s="37"/>
       <c r="D113" s="3" t="s">
         <v>247</v>
       </c>
@@ -3069,9 +3103,9 @@
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A114" s="29"/>
-      <c r="B114" s="30"/>
-      <c r="C114" s="30"/>
+      <c r="A114" s="38"/>
+      <c r="B114" s="37"/>
+      <c r="C114" s="37"/>
       <c r="D114" s="3" t="s">
         <v>248</v>
       </c>
@@ -3080,9 +3114,9 @@
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115" s="29"/>
-      <c r="B115" s="30"/>
-      <c r="C115" s="30"/>
+      <c r="A115" s="38"/>
+      <c r="B115" s="37"/>
+      <c r="C115" s="37"/>
       <c r="D115" s="3" t="s">
         <v>249</v>
       </c>
@@ -3091,13 +3125,13 @@
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A116" s="29" t="s">
+      <c r="A116" s="41" t="s">
         <v>253</v>
       </c>
-      <c r="B116" s="30">
+      <c r="B116" s="42">
         <v>2025</v>
       </c>
-      <c r="C116" s="30"/>
+      <c r="C116" s="37"/>
       <c r="D116" s="3" t="s">
         <v>161</v>
       </c>
@@ -3106,9 +3140,9 @@
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A117" s="29"/>
-      <c r="B117" s="30"/>
-      <c r="C117" s="30"/>
+      <c r="A117" s="41"/>
+      <c r="B117" s="42"/>
+      <c r="C117" s="37"/>
       <c r="D117" s="3" t="s">
         <v>4</v>
       </c>
@@ -3117,9 +3151,9 @@
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A118" s="29"/>
-      <c r="B118" s="30"/>
-      <c r="C118" s="30"/>
+      <c r="A118" s="41"/>
+      <c r="B118" s="42"/>
+      <c r="C118" s="37"/>
       <c r="D118" s="3" t="s">
         <v>251</v>
       </c>
@@ -3128,9 +3162,9 @@
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A119" s="29"/>
-      <c r="B119" s="30"/>
-      <c r="C119" s="30"/>
+      <c r="A119" s="41"/>
+      <c r="B119" s="42"/>
+      <c r="C119" s="37"/>
       <c r="D119" s="3" t="s">
         <v>15</v>
       </c>
@@ -3139,9 +3173,9 @@
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A120" s="29"/>
-      <c r="B120" s="30"/>
-      <c r="C120" s="30"/>
+      <c r="A120" s="41"/>
+      <c r="B120" s="42"/>
+      <c r="C120" s="37"/>
       <c r="D120" s="3" t="s">
         <v>252</v>
       </c>
@@ -3150,9 +3184,9 @@
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A121" s="29"/>
-      <c r="B121" s="30"/>
-      <c r="C121" s="30"/>
+      <c r="A121" s="41"/>
+      <c r="B121" s="42"/>
+      <c r="C121" s="37"/>
       <c r="D121" s="3" t="s">
         <v>176</v>
       </c>
@@ -3161,13 +3195,13 @@
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A122" s="29" t="s">
+      <c r="A122" s="38" t="s">
         <v>271</v>
       </c>
-      <c r="B122" s="30">
+      <c r="B122" s="37">
         <v>2025</v>
       </c>
-      <c r="C122" s="30"/>
+      <c r="C122" s="37"/>
       <c r="D122" s="3" t="s">
         <v>254</v>
       </c>
@@ -3176,9 +3210,9 @@
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A123" s="29"/>
-      <c r="B123" s="30"/>
-      <c r="C123" s="30"/>
+      <c r="A123" s="38"/>
+      <c r="B123" s="37"/>
+      <c r="C123" s="37"/>
       <c r="D123" s="3" t="s">
         <v>52</v>
       </c>
@@ -3187,9 +3221,9 @@
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A124" s="29"/>
-      <c r="B124" s="30"/>
-      <c r="C124" s="30"/>
+      <c r="A124" s="38"/>
+      <c r="B124" s="37"/>
+      <c r="C124" s="37"/>
       <c r="D124" s="3" t="s">
         <v>234</v>
       </c>
@@ -3198,9 +3232,9 @@
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A125" s="29"/>
-      <c r="B125" s="30"/>
-      <c r="C125" s="30"/>
+      <c r="A125" s="38"/>
+      <c r="B125" s="37"/>
+      <c r="C125" s="37"/>
       <c r="D125" s="3" t="s">
         <v>15</v>
       </c>
@@ -3209,9 +3243,9 @@
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A126" s="29"/>
-      <c r="B126" s="30"/>
-      <c r="C126" s="30"/>
+      <c r="A126" s="38"/>
+      <c r="B126" s="37"/>
+      <c r="C126" s="37"/>
       <c r="D126" s="3" t="s">
         <v>19</v>
       </c>
@@ -3220,9 +3254,9 @@
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A127" s="29"/>
-      <c r="B127" s="30"/>
-      <c r="C127" s="30"/>
+      <c r="A127" s="38"/>
+      <c r="B127" s="37"/>
+      <c r="C127" s="37"/>
       <c r="D127" s="3" t="s">
         <v>18</v>
       </c>
@@ -3231,9 +3265,9 @@
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A128" s="29"/>
-      <c r="B128" s="30"/>
-      <c r="C128" s="30"/>
+      <c r="A128" s="38"/>
+      <c r="B128" s="37"/>
+      <c r="C128" s="37"/>
       <c r="D128" s="3" t="s">
         <v>255</v>
       </c>
@@ -3242,9 +3276,9 @@
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A129" s="29"/>
-      <c r="B129" s="30"/>
-      <c r="C129" s="30"/>
+      <c r="A129" s="38"/>
+      <c r="B129" s="37"/>
+      <c r="C129" s="37"/>
       <c r="D129" s="3" t="s">
         <v>256</v>
       </c>
@@ -3253,9 +3287,9 @@
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A130" s="29"/>
-      <c r="B130" s="30"/>
-      <c r="C130" s="30"/>
+      <c r="A130" s="38"/>
+      <c r="B130" s="37"/>
+      <c r="C130" s="37"/>
       <c r="D130" s="3" t="s">
         <v>257</v>
       </c>
@@ -3264,9 +3298,9 @@
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A131" s="29"/>
-      <c r="B131" s="30"/>
-      <c r="C131" s="30"/>
+      <c r="A131" s="38"/>
+      <c r="B131" s="37"/>
+      <c r="C131" s="37"/>
       <c r="D131" s="3" t="s">
         <v>258</v>
       </c>
@@ -3275,9 +3309,9 @@
       </c>
     </row>
     <row r="132" spans="1:5" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="29"/>
-      <c r="B132" s="30"/>
-      <c r="C132" s="30"/>
+      <c r="A132" s="38"/>
+      <c r="B132" s="37"/>
+      <c r="C132" s="37"/>
       <c r="D132" s="3" t="s">
         <v>259</v>
       </c>
@@ -3286,13 +3320,13 @@
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A133" s="29" t="s">
+      <c r="A133" s="38" t="s">
         <v>273</v>
       </c>
-      <c r="B133" s="30">
+      <c r="B133" s="37">
         <v>2025</v>
       </c>
-      <c r="C133" s="30"/>
+      <c r="C133" s="37"/>
       <c r="D133" s="3" t="s">
         <v>17</v>
       </c>
@@ -3301,9 +3335,9 @@
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A134" s="29"/>
-      <c r="B134" s="30"/>
-      <c r="C134" s="30"/>
+      <c r="A134" s="38"/>
+      <c r="B134" s="37"/>
+      <c r="C134" s="37"/>
       <c r="D134" s="3" t="s">
         <v>15</v>
       </c>
@@ -3312,9 +3346,9 @@
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A135" s="29"/>
-      <c r="B135" s="30"/>
-      <c r="C135" s="30"/>
+      <c r="A135" s="38"/>
+      <c r="B135" s="37"/>
+      <c r="C135" s="37"/>
       <c r="D135" s="3" t="s">
         <v>16</v>
       </c>
@@ -3323,9 +3357,9 @@
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A136" s="29"/>
-      <c r="B136" s="30"/>
-      <c r="C136" s="30"/>
+      <c r="A136" s="38"/>
+      <c r="B136" s="37"/>
+      <c r="C136" s="37"/>
       <c r="D136" s="3" t="s">
         <v>272</v>
       </c>
@@ -3334,83 +3368,83 @@
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A137" s="29" t="s">
+      <c r="A137" s="41" t="s">
         <v>276</v>
       </c>
-      <c r="B137" s="30">
+      <c r="B137" s="42">
         <v>2026</v>
       </c>
-      <c r="C137" s="30"/>
-      <c r="D137" s="3" t="s">
+      <c r="C137" s="42"/>
+      <c r="D137" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="E137" s="15">
+      <c r="E137" s="45">
         <v>0.94</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A138" s="29"/>
-      <c r="B138" s="30"/>
-      <c r="C138" s="30"/>
-      <c r="D138" s="3" t="s">
+      <c r="A138" s="41"/>
+      <c r="B138" s="42"/>
+      <c r="C138" s="42"/>
+      <c r="D138" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="E138" s="15">
+      <c r="E138" s="45">
         <v>0.95</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A139" s="29"/>
-      <c r="B139" s="30"/>
-      <c r="C139" s="30"/>
-      <c r="D139" s="3" t="s">
+      <c r="A139" s="41"/>
+      <c r="B139" s="42"/>
+      <c r="C139" s="42"/>
+      <c r="D139" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="E139" s="15">
+      <c r="E139" s="45">
         <v>0.67</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A140" s="29"/>
-      <c r="B140" s="30"/>
-      <c r="C140" s="30"/>
-      <c r="D140" s="3" t="s">
+      <c r="A140" s="41"/>
+      <c r="B140" s="42"/>
+      <c r="C140" s="42"/>
+      <c r="D140" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="E140" s="15">
+      <c r="E140" s="45">
         <v>0.97</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A141" s="29"/>
-      <c r="B141" s="30"/>
-      <c r="C141" s="30"/>
-      <c r="D141" s="3" t="s">
+      <c r="A141" s="41"/>
+      <c r="B141" s="42"/>
+      <c r="C141" s="42"/>
+      <c r="D141" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="E141" s="15">
+      <c r="E141" s="45">
         <v>0.94</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A142" s="29"/>
-      <c r="B142" s="30"/>
-      <c r="C142" s="30"/>
-      <c r="D142" s="3" t="s">
+      <c r="A142" s="41"/>
+      <c r="B142" s="42"/>
+      <c r="C142" s="42"/>
+      <c r="D142" s="44" t="s">
         <v>274</v>
       </c>
-      <c r="E142" s="15">
+      <c r="E142" s="45">
         <v>0.96</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A143" s="29"/>
-      <c r="B143" s="30"/>
-      <c r="C143" s="30"/>
-      <c r="D143" s="3" t="s">
+      <c r="A143" s="41"/>
+      <c r="B143" s="42"/>
+      <c r="C143" s="42"/>
+      <c r="D143" s="44" t="s">
         <v>275</v>
       </c>
-      <c r="E143" s="15">
+      <c r="E143" s="45">
         <v>0.95</v>
       </c>
     </row>
@@ -3801,39 +3835,59 @@
     </row>
   </sheetData>
   <mergeCells count="96">
-    <mergeCell ref="C90:C93"/>
-    <mergeCell ref="B90:B93"/>
-    <mergeCell ref="A90:A93"/>
-    <mergeCell ref="C80:C83"/>
-    <mergeCell ref="B80:B83"/>
-    <mergeCell ref="A80:A83"/>
-    <mergeCell ref="C84:C87"/>
-    <mergeCell ref="B84:B87"/>
-    <mergeCell ref="A84:A87"/>
-    <mergeCell ref="C71:C74"/>
-    <mergeCell ref="B71:B74"/>
-    <mergeCell ref="A71:A74"/>
-    <mergeCell ref="C75:C78"/>
-    <mergeCell ref="B75:B78"/>
-    <mergeCell ref="A75:A78"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="C59:C62"/>
-    <mergeCell ref="B59:B62"/>
-    <mergeCell ref="A59:A62"/>
-    <mergeCell ref="C53:C57"/>
-    <mergeCell ref="B53:B57"/>
-    <mergeCell ref="A53:A57"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="C49:C52"/>
-    <mergeCell ref="B49:B52"/>
-    <mergeCell ref="A49:A52"/>
+    <mergeCell ref="A137:A143"/>
+    <mergeCell ref="B137:B143"/>
+    <mergeCell ref="C137:C143"/>
+    <mergeCell ref="B122:B132"/>
+    <mergeCell ref="C122:C132"/>
+    <mergeCell ref="A122:A132"/>
+    <mergeCell ref="B133:B136"/>
+    <mergeCell ref="C133:C136"/>
+    <mergeCell ref="A133:A136"/>
+    <mergeCell ref="A112:A115"/>
+    <mergeCell ref="B112:B115"/>
+    <mergeCell ref="C112:C115"/>
+    <mergeCell ref="B116:B121"/>
+    <mergeCell ref="A116:A121"/>
+    <mergeCell ref="C116:C121"/>
+    <mergeCell ref="C101:C108"/>
+    <mergeCell ref="B101:B108"/>
+    <mergeCell ref="A101:A108"/>
+    <mergeCell ref="B109:B111"/>
+    <mergeCell ref="A109:A111"/>
+    <mergeCell ref="C109:C111"/>
+    <mergeCell ref="B94:B96"/>
+    <mergeCell ref="C94:C96"/>
+    <mergeCell ref="A94:A96"/>
+    <mergeCell ref="A97:A100"/>
+    <mergeCell ref="B97:B100"/>
+    <mergeCell ref="C97:C100"/>
+    <mergeCell ref="C8:C11"/>
+    <mergeCell ref="C3:C7"/>
+    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="C12:C15"/>
+    <mergeCell ref="B12:B15"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="B32:B34"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="B36:B38"/>
     <mergeCell ref="C44:C46"/>
     <mergeCell ref="B44:B46"/>
     <mergeCell ref="A44:A46"/>
@@ -3844,61 +3898,565 @@
     <mergeCell ref="C42:C43"/>
     <mergeCell ref="B42:B43"/>
     <mergeCell ref="A42:A43"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="B32:B34"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="C36:C38"/>
-    <mergeCell ref="B36:B38"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="A20:A22"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="C12:C15"/>
-    <mergeCell ref="B12:B15"/>
-    <mergeCell ref="A12:A15"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="B16:B18"/>
-    <mergeCell ref="A16:A18"/>
-    <mergeCell ref="C8:C11"/>
-    <mergeCell ref="C3:C7"/>
-    <mergeCell ref="B3:B7"/>
-    <mergeCell ref="A3:A7"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="B94:B96"/>
-    <mergeCell ref="C94:C96"/>
-    <mergeCell ref="A94:A96"/>
-    <mergeCell ref="A97:A100"/>
-    <mergeCell ref="B97:B100"/>
-    <mergeCell ref="C97:C100"/>
-    <mergeCell ref="C101:C108"/>
-    <mergeCell ref="B101:B108"/>
-    <mergeCell ref="A101:A108"/>
-    <mergeCell ref="B109:B111"/>
-    <mergeCell ref="A109:A111"/>
-    <mergeCell ref="C109:C111"/>
-    <mergeCell ref="A112:A115"/>
-    <mergeCell ref="B112:B115"/>
-    <mergeCell ref="C112:C115"/>
-    <mergeCell ref="B116:B121"/>
-    <mergeCell ref="A116:A121"/>
-    <mergeCell ref="C116:C121"/>
-    <mergeCell ref="A137:A143"/>
-    <mergeCell ref="B137:B143"/>
-    <mergeCell ref="C137:C143"/>
-    <mergeCell ref="B122:B132"/>
-    <mergeCell ref="C122:C132"/>
-    <mergeCell ref="A122:A132"/>
-    <mergeCell ref="B133:B136"/>
-    <mergeCell ref="C133:C136"/>
-    <mergeCell ref="A133:A136"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="C49:C52"/>
+    <mergeCell ref="B49:B52"/>
+    <mergeCell ref="A49:A52"/>
+    <mergeCell ref="C59:C62"/>
+    <mergeCell ref="B59:B62"/>
+    <mergeCell ref="A59:A62"/>
+    <mergeCell ref="C53:C57"/>
+    <mergeCell ref="B53:B57"/>
+    <mergeCell ref="A53:A57"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="C71:C74"/>
+    <mergeCell ref="B71:B74"/>
+    <mergeCell ref="A71:A74"/>
+    <mergeCell ref="C75:C78"/>
+    <mergeCell ref="B75:B78"/>
+    <mergeCell ref="A75:A78"/>
+    <mergeCell ref="C90:C93"/>
+    <mergeCell ref="B90:B93"/>
+    <mergeCell ref="A90:A93"/>
+    <mergeCell ref="C80:C83"/>
+    <mergeCell ref="B80:B83"/>
+    <mergeCell ref="A80:A83"/>
+    <mergeCell ref="C84:C87"/>
+    <mergeCell ref="B84:B87"/>
+    <mergeCell ref="A84:A87"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11E209BD-7A28-4777-A415-A49680845E31}">
+  <dimension ref="A2:D47"/>
+  <sheetFormatPr defaultColWidth="26.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="38" t="s">
+        <v>232</v>
+      </c>
+      <c r="B2" s="37">
+        <v>2024</v>
+      </c>
+      <c r="C2" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="32" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="38"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="30" t="s">
+        <v>176</v>
+      </c>
+      <c r="D3" s="32" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="38"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="32" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="38"/>
+      <c r="B5" s="37"/>
+      <c r="C5" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" s="32" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="38"/>
+      <c r="B6" s="37"/>
+      <c r="C6" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="32" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="38"/>
+      <c r="B7" s="37"/>
+      <c r="C7" s="30" t="s">
+        <v>225</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="38"/>
+      <c r="B8" s="37"/>
+      <c r="C8" s="30" t="s">
+        <v>234</v>
+      </c>
+      <c r="D8" s="32" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="38"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="30" t="s">
+        <v>235</v>
+      </c>
+      <c r="D9" s="32" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="38" t="s">
+        <v>232</v>
+      </c>
+      <c r="B10" s="37">
+        <v>2024</v>
+      </c>
+      <c r="C10" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="32" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="38"/>
+      <c r="B11" s="37"/>
+      <c r="C11" s="30" t="s">
+        <v>176</v>
+      </c>
+      <c r="D11" s="32" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="38"/>
+      <c r="B12" s="37"/>
+      <c r="C12" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="32" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="38"/>
+      <c r="B13" s="37"/>
+      <c r="C13" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="32" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="38"/>
+      <c r="B14" s="37"/>
+      <c r="C14" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="32" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="38"/>
+      <c r="B15" s="37"/>
+      <c r="C15" s="30" t="s">
+        <v>225</v>
+      </c>
+      <c r="D15" s="32" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="38"/>
+      <c r="B16" s="37"/>
+      <c r="C16" s="30" t="s">
+        <v>234</v>
+      </c>
+      <c r="D16" s="32" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="38"/>
+      <c r="B17" s="37"/>
+      <c r="C17" s="30" t="s">
+        <v>235</v>
+      </c>
+      <c r="D17" s="32" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="38" t="s">
+        <v>250</v>
+      </c>
+      <c r="B18" s="37">
+        <v>2025</v>
+      </c>
+      <c r="C18" s="30" t="s">
+        <v>246</v>
+      </c>
+      <c r="D18" s="32" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="38"/>
+      <c r="B19" s="37"/>
+      <c r="C19" s="30" t="s">
+        <v>247</v>
+      </c>
+      <c r="D19" s="32" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="38"/>
+      <c r="B20" s="37"/>
+      <c r="C20" s="30" t="s">
+        <v>248</v>
+      </c>
+      <c r="D20" s="32" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="38"/>
+      <c r="B21" s="37"/>
+      <c r="C21" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="D21" s="32" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="38" t="s">
+        <v>271</v>
+      </c>
+      <c r="B22" s="37">
+        <v>2025</v>
+      </c>
+      <c r="C22" s="30" t="s">
+        <v>254</v>
+      </c>
+      <c r="D22" s="9">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="38"/>
+      <c r="B23" s="37"/>
+      <c r="C23" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="D23" s="9">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="38"/>
+      <c r="B24" s="37"/>
+      <c r="C24" s="30" t="s">
+        <v>234</v>
+      </c>
+      <c r="D24" s="9">
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="38"/>
+      <c r="B25" s="37"/>
+      <c r="C25" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="9">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="38"/>
+      <c r="B26" s="37"/>
+      <c r="C26" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" s="9">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="38"/>
+      <c r="B27" s="37"/>
+      <c r="C27" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" s="9">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="38"/>
+      <c r="B28" s="37"/>
+      <c r="C28" s="30" t="s">
+        <v>255</v>
+      </c>
+      <c r="D28" s="32" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="38"/>
+      <c r="B29" s="37"/>
+      <c r="C29" s="30" t="s">
+        <v>256</v>
+      </c>
+      <c r="D29" s="9">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="38"/>
+      <c r="B30" s="37"/>
+      <c r="C30" s="30" t="s">
+        <v>257</v>
+      </c>
+      <c r="D30" s="9">
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="38"/>
+      <c r="B31" s="37"/>
+      <c r="C31" s="30" t="s">
+        <v>258</v>
+      </c>
+      <c r="D31" s="32" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="38"/>
+      <c r="B32" s="37"/>
+      <c r="C32" s="30" t="s">
+        <v>259</v>
+      </c>
+      <c r="D32" s="9">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="38" t="s">
+        <v>273</v>
+      </c>
+      <c r="B33" s="37">
+        <v>2025</v>
+      </c>
+      <c r="C33" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="D33" s="9">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="38"/>
+      <c r="B34" s="37"/>
+      <c r="C34" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" s="9">
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="38"/>
+      <c r="B35" s="37"/>
+      <c r="C35" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="D35" s="9">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="38"/>
+      <c r="B36" s="37"/>
+      <c r="C36" s="30" t="s">
+        <v>272</v>
+      </c>
+      <c r="D36" s="9">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="38" t="s">
+        <v>230</v>
+      </c>
+      <c r="B37" s="37">
+        <v>2024</v>
+      </c>
+      <c r="C37" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="D37" s="30" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="38"/>
+      <c r="B38" s="37"/>
+      <c r="C38" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="D38" s="30" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="38"/>
+      <c r="B39" s="37"/>
+      <c r="C39" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="D39" s="30" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="38"/>
+      <c r="B40" s="37"/>
+      <c r="C40" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="D40" s="30" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="38" t="s">
+        <v>224</v>
+      </c>
+      <c r="B41" s="37">
+        <v>2024</v>
+      </c>
+      <c r="C41" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="D41" s="30" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="38"/>
+      <c r="B42" s="37"/>
+      <c r="C42" s="30" t="s">
+        <v>219</v>
+      </c>
+      <c r="D42" s="32" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="38"/>
+      <c r="B43" s="37"/>
+      <c r="C43" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="D43" s="32" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="38" t="s">
+        <v>191</v>
+      </c>
+      <c r="B44" s="37">
+        <v>2023</v>
+      </c>
+      <c r="C44" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="D44" s="32" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="40"/>
+      <c r="B45" s="37"/>
+      <c r="C45" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="D45" s="32" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="40"/>
+      <c r="B46" s="37"/>
+      <c r="C46" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="D46" s="32" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="142.5" x14ac:dyDescent="0.25">
+      <c r="A47" s="29" t="s">
+        <v>190</v>
+      </c>
+      <c r="B47" s="30">
+        <v>2022</v>
+      </c>
+      <c r="C47" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="D47" s="32" t="s">
+        <v>74</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="A44:A46"/>
+    <mergeCell ref="B44:B46"/>
+    <mergeCell ref="A37:A40"/>
+    <mergeCell ref="B37:B40"/>
+    <mergeCell ref="A41:A43"/>
+    <mergeCell ref="B41:B43"/>
+    <mergeCell ref="A22:A32"/>
+    <mergeCell ref="B22:B32"/>
+    <mergeCell ref="A33:A36"/>
+    <mergeCell ref="B33:B36"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="A10:A17"/>
+    <mergeCell ref="B10:B17"/>
+    <mergeCell ref="A2:A9"/>
+    <mergeCell ref="B2:B9"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>